--- a/2026/YRIGOYEN 7630/Septiembre/YRIGOYEN7630-Septiembre.xlsx
+++ b/2026/YRIGOYEN 7630/Septiembre/YRIGOYEN7630-Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D139AC-06F0-4929-A388-AB7CA9E107F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52228A35-6753-47D6-85A5-8E512CD2D23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,19 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$119</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="132">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -364,36 +359,12 @@
     <t>Gastos part</t>
   </si>
   <si>
-    <t>VTO 17/09</t>
-  </si>
-  <si>
-    <t>PERÍODO: AGOSTO</t>
-  </si>
-  <si>
-    <t>Gustavo padron - Sr contador honorarios AGOSTO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de AGOSTO</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Trabajo cloacal para intentar desobstruir la colectora cloacal</t>
-  </si>
-  <si>
     <t>Cuello Natalia - Limpieza de columna cocina y baño de todas las UF - Cuota 5/5</t>
   </si>
   <si>
     <t>Debito 04/08</t>
   </si>
   <si>
-    <t>Debito 10/08</t>
-  </si>
-  <si>
-    <t>Transf 10/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honorarios administracion - Se adeuda AGOSTO </t>
-  </si>
-  <si>
     <t>Debito 12/08</t>
   </si>
   <si>
@@ -419,6 +390,39 @@
   </si>
   <si>
     <t>Cuota 1/2 - Mamposteria, arreglo administracion anterior</t>
+  </si>
+  <si>
+    <t>VTO 16/10</t>
+  </si>
+  <si>
+    <t>PERÍODO: SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Gustavo padron - Sr contador honorarios SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarios administracion - Se adeuda SEPTIEMBRE </t>
+  </si>
+  <si>
+    <t>Sindicatos mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Transf 28/09</t>
+  </si>
+  <si>
+    <t>Transf 01/09</t>
+  </si>
+  <si>
+    <t>Transf 16/09</t>
+  </si>
+  <si>
+    <t>Transf 11/09</t>
+  </si>
+  <si>
+    <t>Debito 07/09</t>
+  </si>
+  <si>
+    <t>Transf 09/09</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1133,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1403,9 +1407,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="8" fontId="7" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1421,81 +1422,81 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1514,6 +1515,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1592,9 +1597,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1632,9 +1637,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1667,26 +1672,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1719,26 +1707,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1912,22 +1883,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M123"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="68" t="s">
         <v>54</v>
@@ -1936,7 +1907,7 @@
       <c r="D1" s="68"/>
       <c r="E1" s="69"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="70" t="s">
         <v>28</v>
@@ -1945,16 +1916,16 @@
       <c r="D2" s="70"/>
       <c r="E2" s="71"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="215" t="s">
+      <c r="B3" s="210" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="215"/>
-      <c r="D3" s="215"/>
-      <c r="E3" s="216"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="210"/>
+      <c r="D3" s="210"/>
+      <c r="E3" s="211"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -1965,12 +1936,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="70" t="s">
@@ -1978,7 +1949,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>90</v>
       </c>
@@ -1989,62 +1960,62 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="218" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" s="218"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="218"/>
-      <c r="C9" s="218"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="218"/>
-      <c r="C10" s="218"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="217" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="213" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="213"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="213"/>
+      <c r="C9" s="213"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="213"/>
+      <c r="C10" s="213"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="212" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="217"/>
-      <c r="C13" s="217"/>
-      <c r="D13" s="217"/>
-      <c r="E13" s="217"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
-      <c r="B14" s="217"/>
-      <c r="C14" s="217"/>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="217"/>
-      <c r="B15" s="217"/>
-      <c r="C15" s="217"/>
-      <c r="D15" s="217"/>
-      <c r="E15" s="217"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
-      <c r="B16" s="217"/>
-      <c r="C16" s="217"/>
-      <c r="D16" s="217"/>
-      <c r="E16" s="217"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="212"/>
+      <c r="C13" s="212"/>
+      <c r="D13" s="212"/>
+      <c r="E13" s="212"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="212"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="212"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="212"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="212"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D17" s="111"/>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="D18" s="111"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D19" s="111"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>10</v>
       </c>
@@ -2053,7 +2024,7 @@
       <c r="D20" s="115"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
         <v>34</v>
       </c>
@@ -2062,7 +2033,7 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>74</v>
       </c>
@@ -2073,14 +2044,14 @@
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="189"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="56" t="s">
         <v>35</v>
       </c>
@@ -2093,7 +2064,7 @@
       <c r="E24" s="137"/>
       <c r="G24" s="21"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
@@ -2102,7 +2073,7 @@
       <c r="D25" s="189"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>95</v>
       </c>
@@ -2113,7 +2084,7 @@
       </c>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
@@ -2124,7 +2095,7 @@
       </c>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
@@ -2133,7 +2104,7 @@
       <c r="D28" s="191"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="56" t="s">
         <v>35</v>
       </c>
@@ -2145,7 +2116,7 @@
       </c>
       <c r="E29" s="137"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="28" t="s">
         <v>1</v>
       </c>
@@ -2158,7 +2129,7 @@
       </c>
       <c r="F30" s="21"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="34" t="s">
         <v>19</v>
       </c>
@@ -2167,24 +2138,24 @@
       <c r="D31" s="194"/>
       <c r="E31" s="139"/>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="213" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="214"/>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="B32" s="209"/>
       <c r="C32" s="51"/>
-      <c r="D32" s="189">
+      <c r="D32" s="240">
         <v>50000</v>
       </c>
       <c r="E32" s="140"/>
     </row>
-    <row r="33" spans="1:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="213" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" s="214"/>
+    <row r="33" spans="1:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="208" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="209"/>
       <c r="C33" s="51"/>
-      <c r="D33" s="204">
+      <c r="D33" s="203">
         <v>180000</v>
       </c>
       <c r="E33" s="140"/>
@@ -2193,7 +2164,7 @@
       </c>
       <c r="H33" s="149"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="28" t="s">
         <v>16</v>
       </c>
@@ -2205,7 +2176,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="34" t="s">
         <v>31</v>
       </c>
@@ -2214,35 +2185,35 @@
       <c r="D35" s="196"/>
       <c r="E35" s="142"/>
     </row>
-    <row r="36" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="211" t="s">
+    <row r="36" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="214" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="212"/>
+      <c r="B36" s="215"/>
       <c r="C36" s="53"/>
-      <c r="D36" s="205">
+      <c r="D36" s="204">
         <f>30025+7909</f>
         <v>37934</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="213" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="208" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="214"/>
+      <c r="B37" s="209"/>
       <c r="C37" s="53"/>
-      <c r="D37" s="206">
+      <c r="D37" s="205">
         <v>69628</v>
       </c>
-      <c r="E37" s="202" t="str">
+      <c r="E37" s="201" t="str">
         <f>E36</f>
         <v>Debito 04/08</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="28" t="s">
         <v>2</v>
       </c>
@@ -2254,7 +2225,7 @@
         <v>107562</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="34" t="s">
         <v>17</v>
       </c>
@@ -2263,40 +2234,40 @@
       <c r="D39" s="197"/>
       <c r="E39" s="145"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="51"/>
-      <c r="D40" s="207">
-        <v>628219.53</v>
+      <c r="D40" s="241">
+        <v>619750.26</v>
       </c>
       <c r="E40" s="160" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="G40" s="122"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="51"/>
-      <c r="D41" s="207">
+      <c r="D41" s="206">
         <v>10602.27</v>
       </c>
       <c r="E41" s="160" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="51"/>
-      <c r="D42" s="207">
+      <c r="D42" s="206">
         <v>75532.289999999994</v>
       </c>
       <c r="E42" s="151" t="str">
@@ -2309,50 +2280,50 @@
       </c>
       <c r="G42" s="136"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="154">
-        <v>5733.45</v>
+      <c r="D43" s="239">
+        <v>5655.57</v>
       </c>
       <c r="E43" s="160" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="154">
-        <v>99230.87</v>
+      <c r="D44" s="239">
+        <v>98687.47</v>
       </c>
       <c r="E44" s="152" t="str">
         <f>E43</f>
         <v>Debito 12/08</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="154">
-        <v>51601.05</v>
+      <c r="D45" s="239">
+        <v>50900.17</v>
       </c>
       <c r="E45" s="153" t="str">
         <f>E44</f>
         <v>Debito 12/08</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="28" t="s">
         <v>3</v>
       </c>
@@ -2361,10 +2332,10 @@
       <c r="D46" s="198"/>
       <c r="E46" s="143">
         <f>SUM(D40:D45)</f>
-        <v>870919.46000000008</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>861128.03</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="34" t="s">
         <v>18</v>
       </c>
@@ -2373,641 +2344,667 @@
       <c r="D47" s="197"/>
       <c r="E47" s="145"/>
     </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B48" s="154"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="154">
-        <v>46283.07</v>
-      </c>
-      <c r="E48" s="155"/>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="D48" s="239">
+        <v>91685.7</v>
+      </c>
+      <c r="E48" s="155" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
       <c r="B49" s="154"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="154">
-        <v>0</v>
+      <c r="D49" s="239">
+        <v>254864.2</v>
       </c>
       <c r="E49" s="155"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="154"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="239">
+        <v>19854.2</v>
+      </c>
+      <c r="E50" s="155" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B51" s="154"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="239">
+        <v>40698</v>
+      </c>
+      <c r="E51" s="155" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="154">
-        <v>41246.76</v>
-      </c>
-      <c r="E50" s="155" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="211" t="s">
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="239">
+        <v>43083.26</v>
+      </c>
+      <c r="E52" s="155" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="214" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="212"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="154">
+      <c r="B53" s="215"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="239">
         <v>530549.97</v>
       </c>
-      <c r="E51" s="153" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="28" t="s">
+      <c r="E53" s="242" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="199"/>
-      <c r="E52" s="143">
-        <f>SUM(D48:D51)</f>
-        <v>618079.79999999993</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="34" t="s">
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="199"/>
+      <c r="E54" s="143">
+        <f>SUM(D48:D53)</f>
+        <v>980735.33000000007</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="195"/>
-      <c r="E53" s="146"/>
-    </row>
-    <row r="54" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="156" t="s">
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="195"/>
+      <c r="E55" s="146"/>
+    </row>
+    <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="156" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="150"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="154">
+      <c r="B56" s="150"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="239">
         <v>102500</v>
       </c>
-      <c r="E54" s="155" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="156" t="s">
+      <c r="E56" s="155" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="156" t="s">
         <v>93</v>
       </c>
-      <c r="B55" s="150"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="154">
-        <v>0</v>
-      </c>
-      <c r="E55" s="155"/>
-    </row>
-    <row r="56" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="208" t="s">
-        <v>127</v>
-      </c>
-      <c r="B56" s="201"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="105">
+      <c r="B57" s="150"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="154">
+        <v>0</v>
+      </c>
+      <c r="E57" s="155"/>
+    </row>
+    <row r="58" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="207" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" s="150"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="105">
         <f>750000/3</f>
         <v>250000</v>
       </c>
-      <c r="E56" s="203" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="208" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="201"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="105">
-        <v>60000</v>
-      </c>
-      <c r="E57" s="203" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="156" t="s">
-        <v>124</v>
-      </c>
-      <c r="B58" s="201"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="105">
-        <v>78600</v>
-      </c>
-      <c r="E58" s="155" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="211" t="s">
-        <v>115</v>
-      </c>
-      <c r="B59" s="212"/>
+      <c r="E58" s="202" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="207" t="s">
+        <v>120</v>
+      </c>
+      <c r="B59" s="150"/>
       <c r="C59" s="5"/>
       <c r="D59" s="105">
-        <v>333100</v>
-      </c>
-      <c r="E59" s="155" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="211" t="s">
-        <v>114</v>
-      </c>
-      <c r="B60" s="212"/>
+        <v>60000</v>
+      </c>
+      <c r="E59" s="202" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="156" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="150"/>
       <c r="C60" s="5"/>
       <c r="D60" s="105">
-        <v>95700</v>
+        <v>78600</v>
       </c>
       <c r="E60" s="155" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="214" t="s">
+        <v>110</v>
+      </c>
+      <c r="B61" s="215"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="105">
+        <v>333100</v>
+      </c>
+      <c r="E61" s="155" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="214" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" s="215"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="126">
+        <v>60600</v>
+      </c>
+      <c r="E62" s="155" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="34"/>
-      <c r="C61" s="34"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="147">
-        <f>SUM(D54:D60)</f>
-        <v>919900</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="34" t="s">
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="33"/>
+      <c r="E63" s="147">
+        <f>SUM(D56:D62)</f>
+        <v>884800</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="66"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="193"/>
-      <c r="E62" s="146"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
+      <c r="B64" s="66"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="193"/>
+      <c r="E64" s="146"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="154">
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="154">
         <v>67713</v>
       </c>
-      <c r="E63" s="148"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+      <c r="E65" s="148"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="154">
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="154">
         <f>800+168+5112.79+67627.39</f>
         <v>73708.179999999993</v>
       </c>
-      <c r="E64" s="39"/>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="50" t="s">
+      <c r="E66" s="39"/>
+    </row>
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B65" s="50"/>
-      <c r="C65" s="50"/>
-      <c r="D65" s="200"/>
-      <c r="E65" s="102">
-        <f>SUM(D63:D64)</f>
+      <c r="B67" s="50"/>
+      <c r="C67" s="50"/>
+      <c r="D67" s="200"/>
+      <c r="E67" s="102">
+        <f>SUM(D65:D66)</f>
         <v>141421.18</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="101"/>
-      <c r="E66" s="108"/>
-    </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="29" t="s">
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="101"/>
+      <c r="E68" s="108"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="109"/>
-      <c r="E67" s="110">
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="109"/>
+      <c r="E69" s="110">
         <f>4880009.37+700000-3739046.44</f>
         <v>1840962.9300000002</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
-      <c r="D68" s="111"/>
-      <c r="E68" s="112"/>
-      <c r="F68" s="42"/>
-    </row>
-    <row r="69" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="1"/>
+      <c r="D70" s="111"/>
+      <c r="E70" s="112"/>
+      <c r="F70" s="42"/>
+    </row>
+    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="113"/>
-      <c r="E69" s="114">
-        <f>(SUM(E27:E67))</f>
-        <v>5580009.3700000001</v>
-      </c>
-      <c r="F69" s="136">
-        <v>0</v>
-      </c>
-      <c r="G69" s="42"/>
-      <c r="H69" s="122"/>
-      <c r="I69" s="122"/>
-      <c r="J69" s="122"/>
-      <c r="K69" s="122"/>
-      <c r="L69" s="122"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D70" s="111"/>
-      <c r="E70" s="111"/>
-      <c r="H70" s="122"/>
-      <c r="I70" s="122"/>
-      <c r="J70" s="122"/>
-      <c r="K70" s="122"/>
-      <c r="L70" s="122"/>
-    </row>
-    <row r="71" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="111"/>
-      <c r="E71" s="111"/>
-      <c r="H71" s="159"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="10" t="s">
+      <c r="B71" s="9"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="113"/>
+      <c r="E71" s="114">
+        <f>(SUM(E27:E69))</f>
+        <v>5897773.4700000007</v>
+      </c>
+      <c r="F71" s="136">
+        <v>0</v>
+      </c>
+      <c r="G71" s="42"/>
+      <c r="H71" s="122"/>
+      <c r="I71" s="122"/>
+      <c r="J71" s="122"/>
+      <c r="K71" s="122"/>
+      <c r="L71" s="122"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D72" s="111"/>
+      <c r="E72" s="111"/>
+      <c r="H72" s="122"/>
+      <c r="I72" s="122"/>
+      <c r="J72" s="122"/>
+      <c r="K72" s="122"/>
+      <c r="L72" s="122"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D73" s="111"/>
+      <c r="E73" s="111"/>
+      <c r="H73" s="159"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="115"/>
-      <c r="E72" s="116"/>
-    </row>
-    <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="211"/>
-      <c r="B73" s="212"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="126"/>
-      <c r="E73" s="103"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="211"/>
-      <c r="B74" s="212"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="105"/>
-      <c r="E74" s="103"/>
-    </row>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="213"/>
-      <c r="B75" s="214"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="115"/>
+      <c r="E74" s="116"/>
+    </row>
+    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="214"/>
+      <c r="B75" s="215"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="105"/>
+      <c r="D75" s="126"/>
       <c r="E75" s="103"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="104"/>
-      <c r="B76" s="106"/>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="214"/>
+      <c r="B76" s="215"/>
       <c r="C76" s="5"/>
       <c r="D76" s="105"/>
       <c r="E76" s="103"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="48"/>
-      <c r="B77" s="47"/>
-      <c r="C77" s="47"/>
-      <c r="D77" s="57"/>
-      <c r="E77" s="57">
-        <f>SUM(D73:D76)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="29" t="s">
+    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="208"/>
+      <c r="B77" s="209"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="105"/>
+      <c r="E77" s="103"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="104"/>
+      <c r="B78" s="106"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="105"/>
+      <c r="E78" s="103"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="48"/>
+      <c r="B79" s="47"/>
+      <c r="C79" s="47"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57">
+        <f>SUM(D75:D78)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="100"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="100"/>
+    </row>
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B82" s="9"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="67">
-        <f>E77+E80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="98" t="s">
+      <c r="B84" s="9"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="67">
+        <f>E79+E82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="B84" s="99">
-        <f>E69</f>
-        <v>5580009.3700000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="98" t="s">
+      <c r="B86" s="99">
+        <f>E71</f>
+        <v>5897773.4700000007</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B85" s="99">
-        <f>E69-E67</f>
-        <v>3739046.44</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="98" t="s">
+      <c r="B87" s="99">
+        <f>E71-E69</f>
+        <v>4056810.5400000005</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="B86" s="99">
-        <f>E82-E80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="98" t="s">
+      <c r="B88" s="99">
+        <f>E84-E82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="B87" s="99">
-        <f>E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D89" s="122"/>
-      <c r="E89" s="122"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D90" s="122"/>
-      <c r="E90" s="122"/>
-    </row>
-    <row r="91" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="22" t="s">
+      <c r="B89" s="99">
+        <f>E84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D91" s="122"/>
+      <c r="E91" s="122"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D92" s="122"/>
+      <c r="E92" s="122"/>
+    </row>
+    <row r="93" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B91" s="123"/>
-      <c r="C91" s="23"/>
-    </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="32"/>
-      <c r="B92" s="58">
-        <v>0</v>
-      </c>
-      <c r="C92" s="25"/>
-    </row>
-    <row r="93" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="24" t="s">
+      <c r="B93" s="123"/>
+      <c r="C93" s="23"/>
+    </row>
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="32"/>
+      <c r="B94" s="58">
+        <v>0</v>
+      </c>
+      <c r="C94" s="25"/>
+    </row>
+    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B93" s="39">
+      <c r="B95" s="39">
         <f>PRORRATEO!F29</f>
         <v>4938034.42</v>
       </c>
-      <c r="C93" s="23"/>
-    </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="24"/>
-      <c r="B94" s="39">
-        <v>0</v>
-      </c>
-      <c r="C94" s="23"/>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="24" t="s">
+      <c r="C95" s="23"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="24"/>
+      <c r="B96" s="39">
+        <v>0</v>
+      </c>
+      <c r="C96" s="23"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B95" s="107">
-        <f>B116</f>
-        <v>0</v>
-      </c>
-      <c r="C95" s="23"/>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="27"/>
-      <c r="B96" s="46"/>
-      <c r="C96" s="23"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="121" t="s">
+      <c r="B97" s="107">
+        <f>B118</f>
+        <v>0</v>
+      </c>
+      <c r="C97" s="23"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="27"/>
+      <c r="B98" s="46"/>
+      <c r="C98" s="23"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="B97" s="46"/>
-      <c r="C97" s="23"/>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="38" t="s">
+      <c r="B99" s="46"/>
+      <c r="C99" s="23"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B98" s="46">
-        <f>-B85</f>
-        <v>-3739046.44</v>
-      </c>
-      <c r="C98" s="23"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="27" t="s">
+      <c r="B100" s="46">
+        <f>-B87</f>
+        <v>-4056810.5400000005</v>
+      </c>
+      <c r="C100" s="23"/>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B99" s="46">
-        <f>-(B86)</f>
-        <v>0</v>
-      </c>
-      <c r="C99" s="23"/>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="31" t="s">
+      <c r="B101" s="46">
+        <f>-(B88)</f>
+        <v>0</v>
+      </c>
+      <c r="C101" s="23"/>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B100" s="58">
-        <f>SUM(B92:B99)</f>
-        <v>1198987.98</v>
-      </c>
-      <c r="C100" s="26"/>
-      <c r="D100" s="42"/>
-    </row>
-    <row r="101" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="40"/>
-      <c r="C101" s="26"/>
-      <c r="D101" s="42"/>
-      <c r="E101" s="124"/>
-      <c r="F101" s="125"/>
-    </row>
-    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="41"/>
+      <c r="B102" s="58">
+        <f>SUM(B94:B101)</f>
+        <v>881223.87999999942</v>
+      </c>
       <c r="C102" s="26"/>
-    </row>
-    <row r="103" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103"/>
+      <c r="D102" s="42"/>
+    </row>
+    <row r="103" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="40"/>
-      <c r="C103" s="36"/>
-    </row>
-    <row r="104" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="129" t="s">
+      <c r="C103" s="26"/>
+      <c r="D103" s="42"/>
+      <c r="E103" s="124"/>
+      <c r="F103" s="125"/>
+    </row>
+    <row r="104" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B104" s="41"/>
+      <c r="C104" s="26"/>
+    </row>
+    <row r="105" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105"/>
+      <c r="B105" s="40"/>
+      <c r="C105" s="36"/>
+    </row>
+    <row r="106" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="B104" s="165">
+      <c r="B106" s="165">
         <v>-2699002.0460999953</v>
       </c>
-      <c r="C104" s="36"/>
-      <c r="D104" s="45"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="53" t="s">
+      <c r="C106" s="36"/>
+      <c r="D106" s="45"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="B105" s="134">
-        <f>-B85</f>
-        <v>-3739046.44</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="53" t="s">
+      <c r="B107" s="134">
+        <f>-B87</f>
+        <v>-4056810.5400000005</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B106" s="134">
-        <f>-B86</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="53" t="s">
+      <c r="B108" s="134">
+        <f>-B88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="B107" s="134">
-        <f>B116</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="53" t="s">
+      <c r="B109" s="134">
+        <f>B118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="B108" s="135">
+      <c r="B110" s="135">
         <f>PRORRATEO!F29</f>
         <v>4938034.42</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="132" t="s">
+    <row r="111" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="B109" s="133">
-        <f>SUM(B104:C108)</f>
-        <v>-1500014.0660999957</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110" s="130"/>
-      <c r="B110" s="130"/>
-    </row>
-    <row r="111" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="210" t="s">
+      <c r="B111" s="133">
+        <f>SUM(B106:C110)</f>
+        <v>-1817778.1660999954</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="130"/>
+      <c r="B112" s="130"/>
+    </row>
+    <row r="113" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A114" s="217" t="s">
         <v>32</v>
       </c>
-      <c r="B112" s="210"/>
-      <c r="C112" s="210"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="210"/>
-      <c r="B113" s="210"/>
-      <c r="C113" s="210"/>
-    </row>
-    <row r="114" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="118"/>
-      <c r="B114" s="35"/>
-      <c r="C114" s="35">
+      <c r="B114" s="217"/>
+      <c r="C114" s="217"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A115" s="217"/>
+      <c r="B115" s="217"/>
+      <c r="C115" s="217"/>
+    </row>
+    <row r="116" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="118"/>
+      <c r="B116" s="35"/>
+      <c r="C116" s="35">
         <v>40000</v>
       </c>
-      <c r="E114" s="136"/>
-    </row>
-    <row r="115" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="118"/>
-      <c r="B115" s="120"/>
-      <c r="C115" s="117"/>
-      <c r="D115" s="136"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="43" t="s">
+      <c r="E116" s="136"/>
+    </row>
+    <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="118"/>
+      <c r="B117" s="120"/>
+      <c r="C117" s="117"/>
+      <c r="D117" s="136"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B116" s="119">
-        <f>SUM(B114:B115)</f>
-        <v>0</v>
-      </c>
-      <c r="C116" s="44"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M117" s="8"/>
-    </row>
-    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="209"/>
-      <c r="B118" s="209"/>
-      <c r="C118" s="209"/>
-      <c r="D118" s="209"/>
-      <c r="E118" s="209"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="209"/>
-      <c r="B119" s="209"/>
-      <c r="C119" s="209"/>
-      <c r="D119" s="209"/>
-      <c r="E119" s="209"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="209"/>
-      <c r="B120" s="209"/>
-      <c r="C120" s="209"/>
-      <c r="D120" s="209"/>
-      <c r="E120" s="209"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="209"/>
-      <c r="B121" s="209"/>
-      <c r="C121" s="209"/>
-      <c r="D121" s="209"/>
-      <c r="E121" s="209"/>
+      <c r="B118" s="119">
+        <f>SUM(B116:B117)</f>
+        <v>0</v>
+      </c>
+      <c r="C118" s="44"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M119" s="8"/>
+    </row>
+    <row r="120" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="216"/>
+      <c r="B120" s="216"/>
+      <c r="C120" s="216"/>
+      <c r="D120" s="216"/>
+      <c r="E120" s="216"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="216"/>
+      <c r="B121" s="216"/>
+      <c r="C121" s="216"/>
+      <c r="D121" s="216"/>
+      <c r="E121" s="216"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A122" s="216"/>
+      <c r="B122" s="216"/>
+      <c r="C122" s="216"/>
+      <c r="D122" s="216"/>
+      <c r="E122" s="216"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="216"/>
+      <c r="B123" s="216"/>
+      <c r="C123" s="216"/>
+      <c r="D123" s="216"/>
+      <c r="E123" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A120:E123"/>
+    <mergeCell ref="A114:C115"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A118:E121"/>
-    <mergeCell ref="A112:C113"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A75:B75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3018,45 +3015,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="0.140625" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="0.109375" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="226"/>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="220"/>
+      <c r="F1" s="220"/>
+      <c r="G1" s="220"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="220"/>
+      <c r="J1" s="220"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="220"/>
+      <c r="M1" s="220"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3082,7 +3079,7 @@
       <c r="O2" s="54"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3099,77 +3096,77 @@
       <c r="N3" s="55"/>
       <c r="O3" s="59"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="219" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="219" t="s">
+      <c r="B4" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="219" t="s">
+      <c r="C4" s="225" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="219" t="s">
+      <c r="D4" s="225" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="222" t="s">
+      <c r="E4" s="221" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="219" t="s">
+      <c r="F4" s="225" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="229" t="s">
+      <c r="G4" s="227" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="222" t="s">
+      <c r="H4" s="221" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="222" t="s">
+      <c r="I4" s="221" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="222" t="s">
+      <c r="J4" s="221" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="222" t="s">
+      <c r="K4" s="221" t="s">
         <v>109</v>
       </c>
-      <c r="L4" s="232" t="s">
+      <c r="L4" s="230" t="s">
         <v>80</v>
       </c>
       <c r="M4" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="227" t="s">
+      <c r="N4" s="223" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="224" t="s">
+      <c r="O4" s="218" t="s">
         <v>36</v>
       </c>
       <c r="R4" s="128">
         <v>4966143.9300000006</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="221"/>
-      <c r="B5" s="221"/>
-      <c r="C5" s="220"/>
-      <c r="D5" s="221"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="221"/>
-      <c r="G5" s="230"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="231"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="233"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="226"/>
+      <c r="B5" s="226"/>
+      <c r="C5" s="232"/>
+      <c r="D5" s="226"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="229"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="231"/>
       <c r="M5" s="60" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 17/09</v>
-      </c>
-      <c r="N5" s="228"/>
-      <c r="O5" s="225"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 16/10</v>
+      </c>
+      <c r="N5" s="224"/>
+      <c r="O5" s="219"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="161">
         <v>1</v>
       </c>
@@ -3223,7 +3220,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="161">
         <f>A6+1</f>
         <v>2</v>
@@ -3280,7 +3277,7 @@
       </c>
       <c r="Q7" s="42"/>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="161">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
@@ -3335,7 +3332,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="161">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3392,7 +3389,7 @@
       </c>
       <c r="R9" s="42"/>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="161">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3451,7 +3448,7 @@
       </c>
       <c r="R10" s="42"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="161">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3467,7 +3464,7 @@
         <v>234899.06</v>
       </c>
       <c r="F11" s="74">
-        <f>E11+RESUMEN!D56</f>
+        <f>E11+RESUMEN!D58</f>
         <v>484899.06</v>
       </c>
       <c r="G11" s="75">
@@ -3507,7 +3504,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="178">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3562,7 +3559,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="161">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3621,7 +3618,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="161">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3677,7 +3674,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="161">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3733,7 +3730,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="161">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3789,7 +3786,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="161">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3845,7 +3842,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="161">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3901,7 +3898,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="161">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3960,7 +3957,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="161">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -4019,7 +4016,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="63">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -4080,7 +4077,7 @@
       <c r="T21" s="164"/>
       <c r="U21" s="164"/>
     </row>
-    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="63">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -4142,7 +4139,7 @@
       <c r="T22" s="164"/>
       <c r="U22" s="164"/>
     </row>
-    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="63">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -4158,7 +4155,7 @@
         <v>212551.18</v>
       </c>
       <c r="F23" s="74">
-        <f>E23+RESUMEN!D57</f>
+        <f>E23+RESUMEN!D59</f>
         <v>272551.18</v>
       </c>
       <c r="G23" s="75">
@@ -4203,7 +4200,7 @@
       <c r="T23" s="164"/>
       <c r="U23" s="164"/>
     </row>
-    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="63"/>
       <c r="B24" s="63"/>
       <c r="C24" s="64"/>
@@ -4224,7 +4221,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="82"/>
       <c r="B25" s="63"/>
       <c r="C25" s="64"/>
@@ -4242,7 +4239,7 @@
       <c r="O25" s="81"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="1:21" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="82"/>
       <c r="B26" s="65"/>
       <c r="C26" s="64"/>
@@ -4260,7 +4257,7 @@
       <c r="O26" s="81"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="1:21" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="83"/>
       <c r="B27" s="63"/>
       <c r="C27" s="64"/>
@@ -4278,7 +4275,7 @@
       <c r="O27" s="81"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="63"/>
       <c r="B28" s="89"/>
       <c r="C28" s="89"/>
@@ -4296,7 +4293,7 @@
       <c r="O28" s="92"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="93"/>
       <c r="B29" s="94"/>
       <c r="C29" s="94"/>
@@ -4346,100 +4343,106 @@
         <v>10310320.710000001</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="49"/>
       <c r="C30" s="49"/>
     </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="209" t="str">
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="216" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="209"/>
-      <c r="D32" s="209"/>
-      <c r="E32" s="209"/>
-      <c r="F32" s="209"/>
-      <c r="G32" s="209"/>
-      <c r="H32" s="209"/>
-      <c r="I32" s="209"/>
-      <c r="J32" s="209"/>
-      <c r="K32" s="209"/>
-      <c r="L32" s="209"/>
-      <c r="M32" s="209"/>
-    </row>
-    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="209"/>
-      <c r="C33" s="209"/>
-      <c r="D33" s="209"/>
-      <c r="E33" s="209"/>
-      <c r="F33" s="209"/>
-      <c r="G33" s="209"/>
-      <c r="H33" s="209"/>
-      <c r="I33" s="209"/>
-      <c r="J33" s="209"/>
-      <c r="K33" s="209"/>
-      <c r="L33" s="209"/>
-      <c r="M33" s="209"/>
-    </row>
-    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="209"/>
-      <c r="C34" s="209"/>
-      <c r="D34" s="209"/>
-      <c r="E34" s="209"/>
-      <c r="F34" s="209"/>
-      <c r="G34" s="209"/>
-      <c r="H34" s="209"/>
-      <c r="I34" s="209"/>
-      <c r="J34" s="209"/>
-      <c r="K34" s="209"/>
-      <c r="L34" s="209"/>
-      <c r="M34" s="209"/>
-    </row>
-    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="209"/>
-      <c r="C35" s="209"/>
-      <c r="D35" s="209"/>
-      <c r="E35" s="209"/>
-      <c r="F35" s="209"/>
-      <c r="G35" s="209"/>
-      <c r="H35" s="209"/>
-      <c r="I35" s="209"/>
-      <c r="J35" s="209"/>
-      <c r="K35" s="209"/>
-      <c r="L35" s="209"/>
-      <c r="M35" s="209"/>
-    </row>
-    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="209"/>
-      <c r="C36" s="209"/>
-      <c r="D36" s="209"/>
-      <c r="E36" s="209"/>
-      <c r="F36" s="209"/>
-      <c r="G36" s="209"/>
-      <c r="H36" s="209"/>
-      <c r="I36" s="209"/>
-      <c r="J36" s="209"/>
-      <c r="K36" s="209"/>
-      <c r="L36" s="209"/>
-      <c r="M36" s="209"/>
-    </row>
-    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="209"/>
-      <c r="C37" s="209"/>
-      <c r="D37" s="209"/>
-      <c r="E37" s="209"/>
-      <c r="F37" s="209"/>
-      <c r="G37" s="209"/>
-      <c r="H37" s="209"/>
-      <c r="I37" s="209"/>
-      <c r="J37" s="209"/>
-      <c r="K37" s="209"/>
-      <c r="L37" s="209"/>
-      <c r="M37" s="209"/>
+      <c r="C32" s="216"/>
+      <c r="D32" s="216"/>
+      <c r="E32" s="216"/>
+      <c r="F32" s="216"/>
+      <c r="G32" s="216"/>
+      <c r="H32" s="216"/>
+      <c r="I32" s="216"/>
+      <c r="J32" s="216"/>
+      <c r="K32" s="216"/>
+      <c r="L32" s="216"/>
+      <c r="M32" s="216"/>
+    </row>
+    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="216"/>
+      <c r="C33" s="216"/>
+      <c r="D33" s="216"/>
+      <c r="E33" s="216"/>
+      <c r="F33" s="216"/>
+      <c r="G33" s="216"/>
+      <c r="H33" s="216"/>
+      <c r="I33" s="216"/>
+      <c r="J33" s="216"/>
+      <c r="K33" s="216"/>
+      <c r="L33" s="216"/>
+      <c r="M33" s="216"/>
+    </row>
+    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="216"/>
+      <c r="C34" s="216"/>
+      <c r="D34" s="216"/>
+      <c r="E34" s="216"/>
+      <c r="F34" s="216"/>
+      <c r="G34" s="216"/>
+      <c r="H34" s="216"/>
+      <c r="I34" s="216"/>
+      <c r="J34" s="216"/>
+      <c r="K34" s="216"/>
+      <c r="L34" s="216"/>
+      <c r="M34" s="216"/>
+    </row>
+    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="216"/>
+      <c r="C35" s="216"/>
+      <c r="D35" s="216"/>
+      <c r="E35" s="216"/>
+      <c r="F35" s="216"/>
+      <c r="G35" s="216"/>
+      <c r="H35" s="216"/>
+      <c r="I35" s="216"/>
+      <c r="J35" s="216"/>
+      <c r="K35" s="216"/>
+      <c r="L35" s="216"/>
+      <c r="M35" s="216"/>
+    </row>
+    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="216"/>
+      <c r="C36" s="216"/>
+      <c r="D36" s="216"/>
+      <c r="E36" s="216"/>
+      <c r="F36" s="216"/>
+      <c r="G36" s="216"/>
+      <c r="H36" s="216"/>
+      <c r="I36" s="216"/>
+      <c r="J36" s="216"/>
+      <c r="K36" s="216"/>
+      <c r="L36" s="216"/>
+      <c r="M36" s="216"/>
+    </row>
+    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="216"/>
+      <c r="C37" s="216"/>
+      <c r="D37" s="216"/>
+      <c r="E37" s="216"/>
+      <c r="F37" s="216"/>
+      <c r="G37" s="216"/>
+      <c r="H37" s="216"/>
+      <c r="I37" s="216"/>
+      <c r="J37" s="216"/>
+      <c r="K37" s="216"/>
+      <c r="L37" s="216"/>
+      <c r="M37" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="H4:H5"/>
@@ -4450,12 +4453,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="B32:M37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4465,10 +4462,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" s="169" t="s">
         <v>103</v>
       </c>
@@ -4479,7 +4476,7 @@
       <c r="E2" s="166"/>
       <c r="F2" s="167"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B3" s="171" t="s">
         <v>104</v>
       </c>
@@ -4488,58 +4485,58 @@
       </c>
       <c r="F3" s="168"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="234" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="233" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="D4" s="235"/>
-      <c r="E4" s="235"/>
-      <c r="F4" s="236"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="234"/>
-      <c r="C5" s="235"/>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="236"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C4" s="234"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="235"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B5" s="233"/>
+      <c r="C5" s="234"/>
+      <c r="D5" s="234"/>
+      <c r="E5" s="234"/>
+      <c r="F5" s="235"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="122"/>
-      <c r="B6" s="234"/>
-      <c r="C6" s="235"/>
-      <c r="D6" s="235"/>
-      <c r="E6" s="235"/>
-      <c r="F6" s="236"/>
+      <c r="B6" s="233"/>
+      <c r="C6" s="234"/>
+      <c r="D6" s="234"/>
+      <c r="E6" s="234"/>
+      <c r="F6" s="235"/>
       <c r="N6" s="122"/>
       <c r="O6" s="122"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="122"/>
-      <c r="B7" s="234"/>
-      <c r="C7" s="235"/>
-      <c r="D7" s="235"/>
-      <c r="E7" s="235"/>
-      <c r="F7" s="236"/>
+      <c r="B7" s="233"/>
+      <c r="C7" s="234"/>
+      <c r="D7" s="234"/>
+      <c r="E7" s="234"/>
+      <c r="F7" s="235"/>
       <c r="N7" s="122"/>
       <c r="O7" s="122"/>
     </row>
-    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="122"/>
-      <c r="B8" s="237"/>
-      <c r="C8" s="238"/>
-      <c r="D8" s="238"/>
-      <c r="E8" s="238"/>
-      <c r="F8" s="239"/>
+      <c r="B8" s="236"/>
+      <c r="C8" s="237"/>
+      <c r="D8" s="237"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="238"/>
       <c r="N8" s="122"/>
       <c r="O8" s="122"/>
     </row>
-    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="122"/>
       <c r="N9" s="122"/>
       <c r="O9" s="122"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="122"/>
       <c r="B10" s="173" t="s">
         <v>103</v>
@@ -4553,7 +4550,7 @@
       <c r="N10" s="122"/>
       <c r="O10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="122"/>
       <c r="B11" s="175" t="s">
         <v>104</v>
@@ -4565,42 +4562,42 @@
       <c r="N11" s="122"/>
       <c r="O11" s="122"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="234" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B12" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="235"/>
-      <c r="D12" s="235"/>
-      <c r="E12" s="235"/>
-      <c r="F12" s="236"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="234"/>
-      <c r="C13" s="235"/>
-      <c r="D13" s="235"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="236"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="234"/>
-      <c r="C14" s="235"/>
-      <c r="D14" s="235"/>
-      <c r="E14" s="235"/>
-      <c r="F14" s="236"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="234"/>
-      <c r="C15" s="235"/>
-      <c r="D15" s="235"/>
-      <c r="E15" s="235"/>
-      <c r="F15" s="236"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="237"/>
-      <c r="C16" s="238"/>
-      <c r="D16" s="238"/>
-      <c r="E16" s="238"/>
-      <c r="F16" s="239"/>
+      <c r="C12" s="234"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="234"/>
+      <c r="F12" s="235"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="233"/>
+      <c r="C13" s="234"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="234"/>
+      <c r="F13" s="235"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B14" s="233"/>
+      <c r="C14" s="234"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="234"/>
+      <c r="F14" s="235"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B15" s="233"/>
+      <c r="C15" s="234"/>
+      <c r="D15" s="234"/>
+      <c r="E15" s="234"/>
+      <c r="F15" s="235"/>
+    </row>
+    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="236"/>
+      <c r="C16" s="237"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
+      <c r="F16" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/YRIGOYEN 7630/Septiembre/YRIGOYEN7630-Septiembre.xlsx
+++ b/2026/YRIGOYEN 7630/Septiembre/YRIGOYEN7630-Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52228A35-6753-47D6-85A5-8E512CD2D23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7215D625-3085-4A37-B64F-442A1B9C45C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$119</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$116</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="129">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -359,24 +364,9 @@
     <t>Gastos part</t>
   </si>
   <si>
-    <t>Cuello Natalia - Limpieza de columna cocina y baño de todas las UF - Cuota 5/5</t>
-  </si>
-  <si>
-    <t>Debito 04/08</t>
-  </si>
-  <si>
     <t>Debito 12/08</t>
   </si>
   <si>
-    <t>Debito 18/08</t>
-  </si>
-  <si>
-    <t>Transf 18/08</t>
-  </si>
-  <si>
-    <t>Transf 26/08</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
@@ -386,12 +376,6 @@
     <t>Abonado por Dpto 18</t>
   </si>
   <si>
-    <t>Cuota 1/3 - Pintura dpto 6 - Material y mano de obra</t>
-  </si>
-  <si>
-    <t>Cuota 1/2 - Mamposteria, arreglo administracion anterior</t>
-  </si>
-  <si>
     <t>VTO 16/10</t>
   </si>
   <si>
@@ -401,18 +385,12 @@
     <t>Gustavo padron - Sr contador honorarios SEPTIEMBRE</t>
   </si>
   <si>
-    <t xml:space="preserve">Honorarios administracion - Se adeuda SEPTIEMBRE </t>
-  </si>
-  <si>
     <t>Sindicatos mes de SEPTIEMBRE</t>
   </si>
   <si>
     <t>Transf 28/09</t>
   </si>
   <si>
-    <t>Transf 01/09</t>
-  </si>
-  <si>
     <t>Transf 16/09</t>
   </si>
   <si>
@@ -423,6 +401,24 @@
   </si>
   <si>
     <t>Transf 09/09</t>
+  </si>
+  <si>
+    <t>Debito 02/09</t>
+  </si>
+  <si>
+    <t>Transf 07/09</t>
+  </si>
+  <si>
+    <t>Debito 16/09</t>
+  </si>
+  <si>
+    <t>Cuota 2/3 - Pintura dpto 6 - Material y mano de obra</t>
+  </si>
+  <si>
+    <t>Cuota 2/2 - Mamposteria, arreglo administracion anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarios administracion - Mes de Agosto - Se adeuda SEPTIEMBRE </t>
   </si>
 </sst>
 </file>
@@ -439,7 +435,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,6 +631,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -1411,114 +1414,114 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="26" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1597,9 +1600,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1637,9 +1640,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1672,9 +1675,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1707,9 +1727,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1883,22 +1920,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M123"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M120"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="68" t="s">
         <v>54</v>
@@ -1907,7 +1944,7 @@
       <c r="D1" s="68"/>
       <c r="E1" s="69"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="70" t="s">
         <v>28</v>
@@ -1916,16 +1953,16 @@
       <c r="D2" s="70"/>
       <c r="E2" s="71"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="210" t="s">
+      <c r="B3" s="214" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="210"/>
-      <c r="D3" s="210"/>
-      <c r="E3" s="211"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="215"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -1936,12 +1973,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="70" t="s">
@@ -1949,7 +1986,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>90</v>
       </c>
@@ -1960,62 +1997,62 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="213" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="213"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="213"/>
-      <c r="C9" s="213"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="213"/>
-      <c r="C10" s="213"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="212" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="217" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="217"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="216" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="212"/>
-      <c r="C13" s="212"/>
-      <c r="D13" s="212"/>
-      <c r="E13" s="212"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="212"/>
-      <c r="B14" s="212"/>
-      <c r="C14" s="212"/>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="212"/>
-      <c r="B15" s="212"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="212"/>
-      <c r="E15" s="212"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="212"/>
-      <c r="B16" s="212"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="212"/>
-      <c r="E16" s="212"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="216"/>
+      <c r="C13" s="216"/>
+      <c r="D13" s="216"/>
+      <c r="E13" s="216"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="216"/>
+      <c r="B14" s="216"/>
+      <c r="C14" s="216"/>
+      <c r="D14" s="216"/>
+      <c r="E14" s="216"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="216"/>
+      <c r="B15" s="216"/>
+      <c r="C15" s="216"/>
+      <c r="D15" s="216"/>
+      <c r="E15" s="216"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="216"/>
+      <c r="B16" s="216"/>
+      <c r="C16" s="216"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="216"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D17" s="111"/>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="D18" s="111"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D19" s="111"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>10</v>
       </c>
@@ -2024,7 +2061,7 @@
       <c r="D20" s="115"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>34</v>
       </c>
@@ -2033,25 +2070,25 @@
       <c r="D21" s="33"/>
       <c r="E21" s="33"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="189">
-        <v>851164</v>
+      <c r="D22" s="205">
+        <v>890804</v>
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="189"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="56" t="s">
         <v>35</v>
       </c>
@@ -2059,12 +2096,12 @@
       <c r="C24" s="56"/>
       <c r="D24" s="190">
         <f>SUM(D22:D23)</f>
-        <v>851164</v>
+        <v>890804</v>
       </c>
       <c r="E24" s="137"/>
       <c r="G24" s="21"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
@@ -2073,7 +2110,7 @@
       <c r="D25" s="189"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>95</v>
       </c>
@@ -2084,7 +2121,7 @@
       </c>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>96</v>
       </c>
@@ -2095,7 +2132,7 @@
       </c>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
@@ -2104,7 +2141,7 @@
       <c r="D28" s="191"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56" t="s">
         <v>35</v>
       </c>
@@ -2116,7 +2153,7 @@
       </c>
       <c r="E29" s="137"/>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="28" t="s">
         <v>1</v>
       </c>
@@ -2125,11 +2162,11 @@
       <c r="D30" s="193"/>
       <c r="E30" s="138">
         <f>D24+D29</f>
-        <v>851164</v>
+        <v>890804</v>
       </c>
       <c r="F30" s="21"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
         <v>19</v>
       </c>
@@ -2138,33 +2175,35 @@
       <c r="D31" s="194"/>
       <c r="E31" s="139"/>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="208" t="s">
-        <v>123</v>
-      </c>
-      <c r="B32" s="209"/>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="212" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="213"/>
       <c r="C32" s="51"/>
-      <c r="D32" s="240">
+      <c r="D32" s="205">
         <v>50000</v>
       </c>
       <c r="E32" s="140"/>
     </row>
-    <row r="33" spans="1:8" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="208" t="s">
-        <v>124</v>
-      </c>
-      <c r="B33" s="209"/>
+    <row r="33" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="212" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="213"/>
       <c r="C33" s="51"/>
-      <c r="D33" s="203">
+      <c r="D33" s="241">
         <v>180000</v>
       </c>
-      <c r="E33" s="140"/>
+      <c r="E33" s="140" t="s">
+        <v>119</v>
+      </c>
       <c r="G33" s="149" t="s">
         <v>102</v>
       </c>
       <c r="H33" s="149"/>
     </row>
-    <row r="34" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="28" t="s">
         <v>16</v>
       </c>
@@ -2176,7 +2215,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
         <v>31</v>
       </c>
@@ -2185,35 +2224,35 @@
       <c r="D35" s="196"/>
       <c r="E35" s="142"/>
     </row>
-    <row r="36" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="214" t="s">
+    <row r="36" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="210" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="215"/>
+      <c r="B36" s="211"/>
       <c r="C36" s="53"/>
-      <c r="D36" s="204">
+      <c r="D36" s="240">
         <f>30025+7909</f>
         <v>37934</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="208" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="212" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="209"/>
+      <c r="B37" s="213"/>
       <c r="C37" s="53"/>
-      <c r="D37" s="205">
+      <c r="D37" s="239">
         <v>69628</v>
       </c>
       <c r="E37" s="201" t="str">
         <f>E36</f>
-        <v>Debito 04/08</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>Debito 02/09</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="28" t="s">
         <v>2</v>
       </c>
@@ -2225,7 +2264,7 @@
         <v>107562</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="34" t="s">
         <v>17</v>
       </c>
@@ -2234,21 +2273,21 @@
       <c r="D39" s="197"/>
       <c r="E39" s="145"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="51"/>
-      <c r="D40" s="241">
+      <c r="D40" s="206">
         <v>619750.26</v>
       </c>
       <c r="E40" s="160" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G40" s="122"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>77</v>
       </c>
@@ -2258,10 +2297,10 @@
         <v>10602.27</v>
       </c>
       <c r="E41" s="160" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>77</v>
       </c>
@@ -2272,7 +2311,7 @@
       </c>
       <c r="E42" s="151" t="str">
         <f>E41</f>
-        <v>Debito 18/08</v>
+        <v>Debito 16/09</v>
       </c>
       <c r="F42" s="42">
         <f>D42+D41</f>
@@ -2280,27 +2319,27 @@
       </c>
       <c r="G42" s="136"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="239">
+      <c r="D43" s="204">
         <v>5655.57</v>
       </c>
       <c r="E43" s="160" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="239">
+      <c r="D44" s="204">
         <v>98687.47</v>
       </c>
       <c r="E44" s="152" t="str">
@@ -2308,14 +2347,14 @@
         <v>Debito 12/08</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="239">
+      <c r="D45" s="204">
         <v>50900.17</v>
       </c>
       <c r="E45" s="153" t="str">
@@ -2323,7 +2362,7 @@
         <v>Debito 12/08</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="28" t="s">
         <v>3</v>
       </c>
@@ -2335,7 +2374,7 @@
         <v>861128.03</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
         <v>18</v>
       </c>
@@ -2344,667 +2383,629 @@
       <c r="D47" s="197"/>
       <c r="E47" s="145"/>
     </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B48" s="154"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="239">
+      <c r="D48" s="204">
         <v>91685.7</v>
       </c>
       <c r="E48" s="155" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="B49" s="154"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="239">
+      <c r="D49" s="204">
         <v>254864.2</v>
       </c>
-      <c r="E49" s="155"/>
-    </row>
-    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E49" s="155" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B50" s="154"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="239">
+      <c r="D50" s="204">
         <v>19854.2</v>
       </c>
       <c r="E50" s="155" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B51" s="154"/>
+        <v>78</v>
+      </c>
+      <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="239">
-        <v>40698</v>
+      <c r="D51" s="204">
+        <v>43083.26</v>
       </c>
       <c r="E51" s="155" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" s="5"/>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="210" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="211"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="239">
-        <v>43083.26</v>
-      </c>
-      <c r="E52" s="155" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="214" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" s="215"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="239">
+      <c r="D52" s="204">
         <v>530549.97</v>
       </c>
-      <c r="E53" s="242" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="28" t="s">
+      <c r="E52" s="207" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="28" t="s">
         <v>4</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="199"/>
+      <c r="E53" s="143">
+        <f>SUM(D48:D52)</f>
+        <v>940037.33000000007</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="B54" s="28"/>
       <c r="C54" s="28"/>
-      <c r="D54" s="199"/>
-      <c r="E54" s="143">
-        <f>SUM(D48:D53)</f>
-        <v>980735.33000000007</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="195"/>
-      <c r="E55" s="146"/>
-    </row>
-    <row r="56" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D54" s="195"/>
+      <c r="E54" s="146"/>
+    </row>
+    <row r="55" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="156" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="150"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="204">
+        <v>102500</v>
+      </c>
+      <c r="E55" s="155" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="156" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B56" s="150"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="239">
-        <v>102500</v>
-      </c>
-      <c r="E56" s="155" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="156" t="s">
-        <v>93</v>
+      <c r="D56" s="154">
+        <v>0</v>
+      </c>
+      <c r="E56" s="155"/>
+    </row>
+    <row r="57" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="203" t="s">
+        <v>126</v>
       </c>
       <c r="B57" s="150"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="154">
-        <v>0</v>
-      </c>
-      <c r="E57" s="155"/>
-    </row>
-    <row r="58" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="207" t="s">
-        <v>119</v>
+      <c r="D57" s="126">
+        <f>750000/3</f>
+        <v>250000</v>
+      </c>
+      <c r="E57" s="202" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="203" t="s">
+        <v>127</v>
       </c>
       <c r="B58" s="150"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="105">
-        <f>750000/3</f>
-        <v>250000</v>
+      <c r="D58" s="126">
+        <v>60000</v>
       </c>
       <c r="E58" s="202" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="207" t="s">
-        <v>120</v>
-      </c>
-      <c r="B59" s="150"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="210" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" s="211"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="105">
-        <v>60000</v>
-      </c>
-      <c r="E59" s="202" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="156" t="s">
-        <v>116</v>
-      </c>
-      <c r="B60" s="150"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="105">
-        <v>78600</v>
-      </c>
-      <c r="E60" s="155" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="214" t="s">
-        <v>110</v>
-      </c>
-      <c r="B61" s="215"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="105">
-        <v>333100</v>
-      </c>
-      <c r="E61" s="155" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="214" t="s">
-        <v>116</v>
-      </c>
-      <c r="B62" s="215"/>
+      <c r="D59" s="126">
+        <v>60600</v>
+      </c>
+      <c r="E59" s="155" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="147">
+        <f>SUM(D55:D59)</f>
+        <v>473100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="66"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="193"/>
+      <c r="E61" s="146"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="126">
-        <v>60600</v>
-      </c>
-      <c r="E62" s="155" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" s="34"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="147">
-        <f>SUM(D56:D62)</f>
-        <v>884800</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" s="66"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="193"/>
-      <c r="E64" s="146"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
-        <v>87</v>
-      </c>
+      <c r="D62" s="204">
+        <v>67713</v>
+      </c>
+      <c r="E62" s="148"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="204">
+        <v>59676.66</v>
+      </c>
+      <c r="E63" s="39"/>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" s="50"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="200"/>
+      <c r="E64" s="102">
+        <f>SUM(D62:D63)</f>
+        <v>127389.66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
-      <c r="D65" s="154">
-        <v>67713</v>
-      </c>
-      <c r="E65" s="148"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="154">
-        <f>800+168+5112.79+67627.39</f>
-        <v>73708.179999999993</v>
-      </c>
-      <c r="E66" s="39"/>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="B67" s="50"/>
-      <c r="C67" s="50"/>
-      <c r="D67" s="200"/>
-      <c r="E67" s="102">
-        <f>SUM(D65:D66)</f>
-        <v>141421.18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="101"/>
-      <c r="E68" s="108"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="29" t="s">
+      <c r="D65" s="101"/>
+      <c r="E65" s="108"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="109"/>
-      <c r="E69" s="110">
-        <f>4880009.37+700000-3739046.44</f>
-        <v>1840962.9300000002</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="1"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="109"/>
+      <c r="E66" s="110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="D67" s="111"/>
+      <c r="E67" s="112"/>
+      <c r="F67" s="42"/>
+    </row>
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" s="9"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="113"/>
+      <c r="E68" s="114">
+        <f>(SUM(E27:E66))</f>
+        <v>3630021.0200000005</v>
+      </c>
+      <c r="F68" s="136">
+        <v>0</v>
+      </c>
+      <c r="G68" s="42"/>
+      <c r="H68" s="122"/>
+      <c r="I68" s="122"/>
+      <c r="J68" s="122"/>
+      <c r="K68" s="122"/>
+      <c r="L68" s="122"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D69" s="111"/>
+      <c r="E69" s="111"/>
+      <c r="H69" s="122"/>
+      <c r="I69" s="122"/>
+      <c r="J69" s="122"/>
+      <c r="K69" s="122"/>
+      <c r="L69" s="122"/>
+    </row>
+    <row r="70" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D70" s="111"/>
-      <c r="E70" s="112"/>
-      <c r="F70" s="42"/>
-    </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="113"/>
-      <c r="E71" s="114">
-        <f>(SUM(E27:E69))</f>
-        <v>5897773.4700000007</v>
-      </c>
-      <c r="F71" s="136">
-        <v>0</v>
-      </c>
-      <c r="G71" s="42"/>
-      <c r="H71" s="122"/>
-      <c r="I71" s="122"/>
-      <c r="J71" s="122"/>
-      <c r="K71" s="122"/>
-      <c r="L71" s="122"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D72" s="111"/>
-      <c r="E72" s="111"/>
-      <c r="H72" s="122"/>
-      <c r="I72" s="122"/>
-      <c r="J72" s="122"/>
-      <c r="K72" s="122"/>
-      <c r="L72" s="122"/>
-    </row>
-    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D73" s="111"/>
-      <c r="E73" s="111"/>
-      <c r="H73" s="159"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="10" t="s">
+      <c r="E70" s="111"/>
+      <c r="H70" s="159"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B74" s="11"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="115"/>
-      <c r="E74" s="116"/>
-    </row>
-    <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="214"/>
-      <c r="B75" s="215"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="115"/>
+      <c r="E71" s="116"/>
+    </row>
+    <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="210"/>
+      <c r="B72" s="211"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="126"/>
+      <c r="E72" s="103"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="210"/>
+      <c r="B73" s="211"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="105"/>
+      <c r="E73" s="103"/>
+    </row>
+    <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="212"/>
+      <c r="B74" s="213"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="105"/>
+      <c r="E74" s="103"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="104"/>
+      <c r="B75" s="106"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="126"/>
+      <c r="D75" s="105"/>
       <c r="E75" s="103"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="214"/>
-      <c r="B76" s="215"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="105"/>
-      <c r="E76" s="103"/>
-    </row>
-    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="208"/>
-      <c r="B77" s="209"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="105"/>
-      <c r="E77" s="103"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="104"/>
-      <c r="B78" s="106"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="105"/>
-      <c r="E78" s="103"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="48"/>
-      <c r="B79" s="47"/>
-      <c r="C79" s="47"/>
-      <c r="D79" s="57"/>
-      <c r="E79" s="57">
-        <f>SUM(D75:D78)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="29" t="s">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="48"/>
+      <c r="B76" s="47"/>
+      <c r="C76" s="47"/>
+      <c r="D76" s="57"/>
+      <c r="E76" s="57">
+        <f>SUM(D72:D75)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="1:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="100"/>
-    </row>
-    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="100"/>
+    </row>
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B84" s="9"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="67">
-        <f>E79+E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="9"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="67">
+        <f>E76+E79</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="98" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="99">
+        <f>E68</f>
+        <v>3630021.0200000005</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" s="99">
+        <f>E68-E66</f>
+        <v>3630021.0200000005</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="98" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="99">
+        <f>E81-E79</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="98" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B86" s="99">
-        <f>E71</f>
-        <v>5897773.4700000007</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" s="99">
-        <f>E71-E69</f>
-        <v>4056810.5400000005</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="99">
-        <f>E84-E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="98" t="s">
-        <v>40</v>
-      </c>
-      <c r="B89" s="99">
-        <f>E84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D91" s="122"/>
-      <c r="E91" s="122"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D92" s="122"/>
-      <c r="E92" s="122"/>
-    </row>
-    <row r="93" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="22" t="s">
+        <f>E81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D88" s="122"/>
+      <c r="E88" s="122"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D89" s="122"/>
+      <c r="E89" s="122"/>
+    </row>
+    <row r="90" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B93" s="123"/>
+      <c r="B90" s="123"/>
+      <c r="C90" s="23"/>
+    </row>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="32"/>
+      <c r="B91" s="58">
+        <v>0</v>
+      </c>
+      <c r="C91" s="25"/>
+    </row>
+    <row r="92" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="39">
+        <f>PRORRATEO!F29</f>
+        <v>4404558.63</v>
+      </c>
+      <c r="C92" s="23"/>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="24"/>
+      <c r="B93" s="39">
+        <v>0</v>
+      </c>
       <c r="C93" s="23"/>
     </row>
-    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="32"/>
-      <c r="B94" s="58">
-        <v>0</v>
-      </c>
-      <c r="C94" s="25"/>
-    </row>
-    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B95" s="39">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="107">
+        <f>B115</f>
+        <v>0</v>
+      </c>
+      <c r="C94" s="23"/>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="27"/>
+      <c r="B95" s="46"/>
+      <c r="C95" s="23"/>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="121" t="s">
+        <v>46</v>
+      </c>
+      <c r="B96" s="46"/>
+      <c r="C96" s="23"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B97" s="46">
+        <f>-B84</f>
+        <v>-3630021.0200000005</v>
+      </c>
+      <c r="C97" s="23"/>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B98" s="46">
+        <f>-(B85)</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="23"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="58">
+        <f>SUM(B91:B98)</f>
+        <v>774537.6099999994</v>
+      </c>
+      <c r="C99" s="26"/>
+      <c r="D99" s="42"/>
+    </row>
+    <row r="100" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="40"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="42"/>
+      <c r="E100" s="124"/>
+      <c r="F100" s="125"/>
+    </row>
+    <row r="101" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="41"/>
+      <c r="C101" s="26"/>
+    </row>
+    <row r="102" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102"/>
+      <c r="B102" s="40"/>
+      <c r="C102" s="36"/>
+    </row>
+    <row r="103" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="129" t="s">
+        <v>85</v>
+      </c>
+      <c r="B103" s="165">
+        <v>-1500014.0660999957</v>
+      </c>
+      <c r="C103" s="36"/>
+      <c r="D103" s="45"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B104" s="134">
+        <f>-B84</f>
+        <v>-3630021.0200000005</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B105" s="134">
+        <f>-B85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" s="134">
+        <f>B115</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B107" s="135">
         <f>PRORRATEO!F29</f>
-        <v>4938034.42</v>
-      </c>
-      <c r="C95" s="23"/>
-    </row>
-    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="24"/>
-      <c r="B96" s="39">
-        <v>0</v>
-      </c>
-      <c r="C96" s="23"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B97" s="107">
-        <f>B118</f>
-        <v>0</v>
-      </c>
-      <c r="C97" s="23"/>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="27"/>
-      <c r="B98" s="46"/>
-      <c r="C98" s="23"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="121" t="s">
-        <v>46</v>
-      </c>
-      <c r="B99" s="46"/>
-      <c r="C99" s="23"/>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B100" s="46">
-        <f>-B87</f>
-        <v>-4056810.5400000005</v>
-      </c>
-      <c r="C100" s="23"/>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B101" s="46">
-        <f>-(B88)</f>
-        <v>0</v>
-      </c>
-      <c r="C101" s="23"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="31" t="s">
+        <v>4404558.63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="132" t="s">
+        <v>48</v>
+      </c>
+      <c r="B108" s="133">
+        <f>SUM(B103:C107)</f>
+        <v>-725476.45609999634</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="130"/>
+      <c r="B109" s="130"/>
+    </row>
+    <row r="110" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="209" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111" s="209"/>
+      <c r="C111" s="209"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="209"/>
+      <c r="B112" s="209"/>
+      <c r="C112" s="209"/>
+    </row>
+    <row r="113" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="118"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="35">
+        <v>40000</v>
+      </c>
+      <c r="E113" s="136"/>
+    </row>
+    <row r="114" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="118"/>
+      <c r="B114" s="120"/>
+      <c r="C114" s="117"/>
+      <c r="D114" s="136"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B102" s="58">
-        <f>SUM(B94:B101)</f>
-        <v>881223.87999999942</v>
-      </c>
-      <c r="C102" s="26"/>
-      <c r="D102" s="42"/>
-    </row>
-    <row r="103" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="40"/>
-      <c r="C103" s="26"/>
-      <c r="D103" s="42"/>
-      <c r="E103" s="124"/>
-      <c r="F103" s="125"/>
-    </row>
-    <row r="104" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="41"/>
-      <c r="C104" s="26"/>
-    </row>
-    <row r="105" spans="1:6" s="37" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105"/>
-      <c r="B105" s="40"/>
-      <c r="C105" s="36"/>
-    </row>
-    <row r="106" spans="1:6" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="129" t="s">
-        <v>85</v>
-      </c>
-      <c r="B106" s="165">
-        <v>-2699002.0460999953</v>
-      </c>
-      <c r="C106" s="36"/>
-      <c r="D106" s="45"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="B107" s="134">
-        <f>-B87</f>
-        <v>-4056810.5400000005</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B108" s="134">
-        <f>-B88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="B109" s="134">
-        <f>B118</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B110" s="135">
-        <f>PRORRATEO!F29</f>
-        <v>4938034.42</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="132" t="s">
-        <v>48</v>
-      </c>
-      <c r="B111" s="133">
-        <f>SUM(B106:C110)</f>
-        <v>-1817778.1660999954</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="130"/>
-      <c r="B112" s="130"/>
-    </row>
-    <row r="113" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="217" t="s">
-        <v>32</v>
-      </c>
-      <c r="B114" s="217"/>
-      <c r="C114" s="217"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="217"/>
-      <c r="B115" s="217"/>
-      <c r="C115" s="217"/>
-    </row>
-    <row r="116" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="118"/>
-      <c r="B116" s="35"/>
-      <c r="C116" s="35">
-        <v>40000</v>
-      </c>
-      <c r="E116" s="136"/>
-    </row>
-    <row r="117" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="118"/>
-      <c r="B117" s="120"/>
-      <c r="C117" s="117"/>
-      <c r="D117" s="136"/>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="B118" s="119">
-        <f>SUM(B116:B117)</f>
-        <v>0</v>
-      </c>
-      <c r="C118" s="44"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M119" s="8"/>
-    </row>
-    <row r="120" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="216"/>
-      <c r="B120" s="216"/>
-      <c r="C120" s="216"/>
-      <c r="D120" s="216"/>
-      <c r="E120" s="216"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="216"/>
-      <c r="B121" s="216"/>
-      <c r="C121" s="216"/>
-      <c r="D121" s="216"/>
-      <c r="E121" s="216"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="216"/>
-      <c r="B122" s="216"/>
-      <c r="C122" s="216"/>
-      <c r="D122" s="216"/>
-      <c r="E122" s="216"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="216"/>
-      <c r="B123" s="216"/>
-      <c r="C123" s="216"/>
-      <c r="D123" s="216"/>
-      <c r="E123" s="216"/>
+      <c r="B115" s="119">
+        <f>SUM(B113:B114)</f>
+        <v>0</v>
+      </c>
+      <c r="C115" s="44"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M116" s="8"/>
+    </row>
+    <row r="117" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="208"/>
+      <c r="B117" s="208"/>
+      <c r="C117" s="208"/>
+      <c r="D117" s="208"/>
+      <c r="E117" s="208"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="208"/>
+      <c r="B118" s="208"/>
+      <c r="C118" s="208"/>
+      <c r="D118" s="208"/>
+      <c r="E118" s="208"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="208"/>
+      <c r="B119" s="208"/>
+      <c r="C119" s="208"/>
+      <c r="D119" s="208"/>
+      <c r="E119" s="208"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="208"/>
+      <c r="B120" s="208"/>
+      <c r="C120" s="208"/>
+      <c r="D120" s="208"/>
+      <c r="E120" s="208"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A120:E123"/>
-    <mergeCell ref="A114:C115"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A61:B61"/>
+  <mergeCells count="14">
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A117:E120"/>
+    <mergeCell ref="A111:C112"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A74:B74"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3015,45 +3016,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.33203125" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="0.109375" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="0.140625" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="220"/>
-      <c r="E1" s="220"/>
-      <c r="F1" s="220"/>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="220"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="225"/>
+      <c r="F1" s="225"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3079,7 +3080,7 @@
       <c r="O2" s="54"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3096,26 +3097,26 @@
       <c r="N3" s="55"/>
       <c r="O3" s="59"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="225" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="225" t="s">
+      <c r="B4" s="218" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="225" t="s">
+      <c r="C4" s="218" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="218" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="221" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="225" t="s">
+      <c r="F4" s="218" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="227" t="s">
+      <c r="G4" s="228" t="s">
         <v>30</v>
       </c>
       <c r="H4" s="221" t="s">
@@ -3130,43 +3131,43 @@
       <c r="K4" s="221" t="s">
         <v>109</v>
       </c>
-      <c r="L4" s="230" t="s">
+      <c r="L4" s="231" t="s">
         <v>80</v>
       </c>
       <c r="M4" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="223" t="s">
+      <c r="N4" s="226" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="218" t="s">
+      <c r="O4" s="223" t="s">
         <v>36</v>
       </c>
       <c r="R4" s="128">
         <v>4966143.9300000006</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="226"/>
-      <c r="B5" s="226"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="226"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="220"/>
+      <c r="B5" s="220"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="220"/>
       <c r="E5" s="222"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="228"/>
+      <c r="F5" s="220"/>
+      <c r="G5" s="229"/>
       <c r="H5" s="222"/>
-      <c r="I5" s="229"/>
+      <c r="I5" s="230"/>
       <c r="J5" s="222"/>
       <c r="K5" s="222"/>
-      <c r="L5" s="231"/>
+      <c r="L5" s="232"/>
       <c r="M5" s="60" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="N5" s="224"/>
-      <c r="O5" s="219"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N5" s="227"/>
+      <c r="O5" s="224"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="161">
         <v>1</v>
       </c>
@@ -3178,11 +3179,11 @@
         <v>6.69</v>
       </c>
       <c r="E6" s="73">
-        <v>332235.01</v>
-      </c>
-      <c r="F6" s="74">
+        <v>379065.01</v>
+      </c>
+      <c r="F6" s="242">
         <f>E6</f>
-        <v>332235.01</v>
+        <v>379065.01</v>
       </c>
       <c r="G6" s="75">
         <f t="shared" ref="G6:G23" si="0">E6-F6</f>
@@ -3220,7 +3221,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="161">
         <f>A6+1</f>
         <v>2</v>
@@ -3233,16 +3234,16 @@
         <v>5.88</v>
       </c>
       <c r="E7" s="73">
-        <v>2898882.02</v>
+        <v>3442518.02</v>
       </c>
       <c r="F7" s="74"/>
       <c r="G7" s="75">
         <f t="shared" si="0"/>
-        <v>2898882.02</v>
+        <v>3442518.02</v>
       </c>
       <c r="H7" s="75">
         <f t="shared" ref="H7:H23" si="2">IF(G7&gt;0,G7*3%,0)</f>
-        <v>86966.460599999991</v>
+        <v>103275.54059999999</v>
       </c>
       <c r="I7" s="76">
         <v>0</v>
@@ -3261,15 +3262,15 @@
       </c>
       <c r="M7" s="79">
         <f t="shared" ref="M7:M23" si="4">ROUND(SUM(G7:L7),0) + P7</f>
-        <v>3442518.02</v>
+        <v>4002463.02</v>
       </c>
       <c r="N7" s="80">
         <f t="shared" ref="N7:N23" si="5">ROUND(M7*6% + M7,0) + P7</f>
-        <v>3649069.02</v>
+        <v>4242611.0199999996</v>
       </c>
       <c r="O7" s="81">
         <f t="shared" ref="O7:O23" si="6">ROUND(M7*3%,0) + M7</f>
-        <v>3545794.02</v>
+        <v>4122537.02</v>
       </c>
       <c r="P7" s="42">
         <f>P6+0.01</f>
@@ -3277,7 +3278,7 @@
       </c>
       <c r="Q7" s="42"/>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="161">
         <f t="shared" ref="A8:A23" si="7">A7+1</f>
         <v>3</v>
@@ -3290,18 +3291,18 @@
         <v>6.65</v>
       </c>
       <c r="E8" s="74">
-        <v>560853.03</v>
-      </c>
-      <c r="F8" s="74">
-        <v>0</v>
+        <v>954477.03</v>
+      </c>
+      <c r="F8" s="242">
+        <v>400000.03</v>
       </c>
       <c r="G8" s="75">
         <f t="shared" si="0"/>
-        <v>560853.03</v>
+        <v>554477</v>
       </c>
       <c r="H8" s="75">
         <f t="shared" si="2"/>
-        <v>16825.590899999999</v>
+        <v>16634.309999999998</v>
       </c>
       <c r="I8" s="76">
         <v>0</v>
@@ -3317,22 +3318,22 @@
       </c>
       <c r="M8" s="79">
         <f t="shared" si="4"/>
-        <v>954477.03</v>
+        <v>947910.03</v>
       </c>
       <c r="N8" s="80">
         <f t="shared" si="5"/>
-        <v>1011746.03</v>
+        <v>1004785.03</v>
       </c>
       <c r="O8" s="81">
         <f t="shared" si="6"/>
-        <v>983111.03</v>
+        <v>976347.03</v>
       </c>
       <c r="P8" s="42">
         <f t="shared" ref="P8:P24" si="8">P7+0.01</f>
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="161">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -3345,11 +3346,11 @@
         <v>6.73</v>
       </c>
       <c r="E9" s="73">
-        <v>334221.03999999998</v>
-      </c>
-      <c r="F9" s="74">
+        <v>381331.04</v>
+      </c>
+      <c r="F9" s="242">
         <f>E9</f>
-        <v>334221.03999999998</v>
+        <v>381331.04</v>
       </c>
       <c r="G9" s="75">
         <f t="shared" si="0"/>
@@ -3389,7 +3390,7 @@
       </c>
       <c r="R9" s="42"/>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="161">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -3402,18 +3403,18 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="73">
-        <v>834850.05</v>
+        <v>455558.05</v>
       </c>
       <c r="F10" s="74">
-        <v>834850.05</v>
+        <v>0</v>
       </c>
       <c r="G10" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>455558.05</v>
       </c>
       <c r="H10" s="75">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>13666.741499999998</v>
       </c>
       <c r="I10" s="76">
         <v>0</v>
@@ -3429,15 +3430,15 @@
       </c>
       <c r="M10" s="79">
         <f t="shared" si="4"/>
-        <v>455558.05</v>
+        <v>924783.05</v>
       </c>
       <c r="N10" s="80">
         <f t="shared" si="5"/>
-        <v>482892.05</v>
+        <v>980270.05</v>
       </c>
       <c r="O10" s="81">
         <f t="shared" si="6"/>
-        <v>469225.05</v>
+        <v>952526.05</v>
       </c>
       <c r="P10" s="42">
         <f t="shared" si="8"/>
@@ -3448,7 +3449,7 @@
       </c>
       <c r="R10" s="42"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="161">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -3461,11 +3462,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="E11" s="73">
-        <v>234899.06</v>
-      </c>
-      <c r="F11" s="74">
-        <f>E11+RESUMEN!D58</f>
-        <v>484899.06</v>
+        <v>18009.060000000001</v>
+      </c>
+      <c r="F11" s="242">
+        <f>E11+RESUMEN!D57</f>
+        <v>268009.06</v>
       </c>
       <c r="G11" s="75">
         <f t="shared" si="0"/>
@@ -3504,7 +3505,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="178">
         <f t="shared" si="7"/>
         <v>7</v>
@@ -3517,18 +3518,18 @@
         <v>5.67</v>
       </c>
       <c r="E12" s="180">
-        <v>1048899.07</v>
+        <v>1144136.07</v>
       </c>
       <c r="F12" s="180">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="182">
         <f t="shared" si="0"/>
-        <v>798899.07000000007</v>
+        <v>1144136.07</v>
       </c>
       <c r="H12" s="182">
         <f t="shared" si="2"/>
-        <v>23966.972100000003</v>
+        <v>34324.0821</v>
       </c>
       <c r="I12" s="181">
         <v>0</v>
@@ -3544,22 +3545,22 @@
       </c>
       <c r="M12" s="185">
         <f t="shared" si="4"/>
-        <v>1144136.07</v>
+        <v>1499731.07</v>
       </c>
       <c r="N12" s="186">
         <f t="shared" si="5"/>
-        <v>1212784.07</v>
+        <v>1589715.07</v>
       </c>
       <c r="O12" s="187">
         <f t="shared" si="6"/>
-        <v>1178460.07</v>
+        <v>1544723.07</v>
       </c>
       <c r="P12" s="42">
         <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="161">
         <f t="shared" si="7"/>
         <v>8</v>
@@ -3572,19 +3573,18 @@
         <v>5.67</v>
       </c>
       <c r="E13" s="73">
-        <v>281580.08</v>
+        <v>321270.08</v>
       </c>
       <c r="F13" s="74">
-        <f t="shared" ref="F13:F18" si="9">E13</f>
-        <v>281580.08</v>
+        <v>0</v>
       </c>
       <c r="G13" s="75">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>321270.08</v>
       </c>
       <c r="H13" s="75">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9638.1023999999998</v>
       </c>
       <c r="I13" s="76">
         <v>0</v>
@@ -3600,15 +3600,15 @@
       </c>
       <c r="M13" s="79">
         <f t="shared" si="4"/>
-        <v>321270.08</v>
+        <v>652179.07999999996</v>
       </c>
       <c r="N13" s="80">
         <f t="shared" si="5"/>
-        <v>340546.08</v>
+        <v>691310.07999999996</v>
       </c>
       <c r="O13" s="81">
         <f t="shared" si="6"/>
-        <v>330908.08</v>
+        <v>671744.08</v>
       </c>
       <c r="P13" s="42">
         <f t="shared" si="8"/>
@@ -3618,7 +3618,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="161">
         <f t="shared" si="7"/>
         <v>9</v>
@@ -3631,11 +3631,11 @@
         <v>7.67</v>
       </c>
       <c r="E14" s="73">
-        <v>380903.09</v>
-      </c>
-      <c r="F14" s="74">
-        <f t="shared" si="9"/>
-        <v>380903.09</v>
+        <v>434593.09</v>
+      </c>
+      <c r="F14" s="242">
+        <f>E14</f>
+        <v>434593.09</v>
       </c>
       <c r="G14" s="75">
         <f t="shared" si="0"/>
@@ -3674,7 +3674,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="161">
         <f t="shared" si="7"/>
         <v>10</v>
@@ -3687,11 +3687,11 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="73">
-        <v>243341.1</v>
-      </c>
-      <c r="F15" s="74">
-        <f t="shared" si="9"/>
-        <v>243341.1</v>
+        <v>277641.09999999998</v>
+      </c>
+      <c r="F15" s="242">
+        <f>E15</f>
+        <v>277641.09999999998</v>
       </c>
       <c r="G15" s="75">
         <f t="shared" si="0"/>
@@ -3730,7 +3730,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="161">
         <f t="shared" si="7"/>
         <v>11</v>
@@ -3743,11 +3743,11 @@
         <v>5.63</v>
       </c>
       <c r="E16" s="73">
-        <v>288234.11</v>
-      </c>
-      <c r="F16" s="74">
-        <f t="shared" si="9"/>
-        <v>288234.11</v>
+        <v>319004.11</v>
+      </c>
+      <c r="F16" s="242">
+        <f>E16</f>
+        <v>319004.11</v>
       </c>
       <c r="G16" s="75">
         <f t="shared" si="0"/>
@@ -3786,7 +3786,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="161">
         <f t="shared" si="7"/>
         <v>12</v>
@@ -3799,11 +3799,11 @@
         <v>5.55</v>
       </c>
       <c r="E17" s="73">
-        <v>275621.12</v>
-      </c>
-      <c r="F17" s="74">
-        <f t="shared" si="9"/>
-        <v>275621.12</v>
+        <v>314471.12</v>
+      </c>
+      <c r="F17" s="242">
+        <f t="shared" ref="F13:F18" si="9">E17</f>
+        <v>314471.12</v>
       </c>
       <c r="G17" s="75">
         <f t="shared" si="0"/>
@@ -3842,7 +3842,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="161">
         <f t="shared" si="7"/>
         <v>13</v>
@@ -3855,11 +3855,11 @@
         <v>11.06</v>
       </c>
       <c r="E18" s="73">
-        <v>549256.13</v>
-      </c>
-      <c r="F18" s="74">
-        <f t="shared" si="9"/>
-        <v>549256.13</v>
+        <v>626676.13</v>
+      </c>
+      <c r="F18" s="242">
+        <f>E18</f>
+        <v>626676.13</v>
       </c>
       <c r="G18" s="75">
         <f t="shared" si="0"/>
@@ -3898,7 +3898,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="161">
         <f t="shared" si="7"/>
         <v>14</v>
@@ -3911,19 +3911,19 @@
         <v>3.3</v>
       </c>
       <c r="E19" s="73">
-        <v>166811.14000000001</v>
-      </c>
-      <c r="F19" s="74">
-        <f>1+161040.14</f>
-        <v>161041.14000000001</v>
+        <v>192926.14</v>
+      </c>
+      <c r="F19" s="242">
+        <f>184140.14+2842.14</f>
+        <v>186982.28000000003</v>
       </c>
       <c r="G19" s="75">
         <f t="shared" si="0"/>
-        <v>5770</v>
+        <v>5943.859999999986</v>
       </c>
       <c r="H19" s="75">
         <f t="shared" si="2"/>
-        <v>173.1</v>
+        <v>178.31579999999957</v>
       </c>
       <c r="I19" s="76">
         <v>0</v>
@@ -3939,15 +3939,15 @@
       </c>
       <c r="M19" s="79">
         <f t="shared" si="4"/>
-        <v>192926.14</v>
+        <v>193105.14</v>
       </c>
       <c r="N19" s="80">
         <f t="shared" si="5"/>
-        <v>204502.14</v>
+        <v>204691.14</v>
       </c>
       <c r="O19" s="81">
         <f t="shared" si="6"/>
-        <v>198714.14</v>
+        <v>198898.14</v>
       </c>
       <c r="P19" s="42">
         <f t="shared" si="8"/>
@@ -3957,7 +3957,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="161">
         <f t="shared" si="7"/>
         <v>15</v>
@@ -3970,11 +3970,11 @@
         <v>1.8</v>
       </c>
       <c r="E20" s="74">
-        <v>89391.15</v>
-      </c>
-      <c r="F20" s="74">
+        <v>101991.15</v>
+      </c>
+      <c r="F20" s="242">
         <f>E20</f>
-        <v>89391.15</v>
+        <v>101991.15</v>
       </c>
       <c r="G20" s="75">
         <f t="shared" si="0"/>
@@ -4016,7 +4016,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="63">
         <f t="shared" si="7"/>
         <v>16</v>
@@ -4029,11 +4029,11 @@
         <v>3.22</v>
       </c>
       <c r="E21" s="73">
-        <v>159910.16</v>
-      </c>
-      <c r="F21" s="74">
-        <f t="shared" ref="F21" si="10">E21</f>
-        <v>159910.16</v>
+        <v>182450.16</v>
+      </c>
+      <c r="F21" s="242">
+        <f>E21</f>
+        <v>182450.16</v>
       </c>
       <c r="G21" s="75">
         <f t="shared" si="0"/>
@@ -4077,7 +4077,7 @@
       <c r="T21" s="164"/>
       <c r="U21" s="164"/>
     </row>
-    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="63">
         <f t="shared" si="7"/>
         <v>17</v>
@@ -4090,18 +4090,19 @@
         <v>2.61</v>
       </c>
       <c r="E22" s="74">
-        <v>129616.17</v>
-      </c>
-      <c r="F22" s="74">
-        <v>0</v>
+        <v>289833.17</v>
+      </c>
+      <c r="F22" s="242">
+        <f>E22</f>
+        <v>289833.17</v>
       </c>
       <c r="G22" s="75">
         <f t="shared" si="0"/>
-        <v>129616.17</v>
+        <v>0</v>
       </c>
       <c r="H22" s="75">
         <f t="shared" si="2"/>
-        <v>3888.4850999999999</v>
+        <v>0</v>
       </c>
       <c r="I22" s="76">
         <v>0</v>
@@ -4117,15 +4118,15 @@
       </c>
       <c r="M22" s="79">
         <f t="shared" si="4"/>
-        <v>281391.17</v>
+        <v>147886.17000000001</v>
       </c>
       <c r="N22" s="80">
         <f t="shared" si="5"/>
-        <v>298275.17</v>
+        <v>156759.17000000001</v>
       </c>
       <c r="O22" s="81">
         <f t="shared" si="6"/>
-        <v>289833.17</v>
+        <v>152323.17000000001</v>
       </c>
       <c r="P22" s="42">
         <f t="shared" si="8"/>
@@ -4139,7 +4140,7 @@
       <c r="T22" s="164"/>
       <c r="U22" s="164"/>
     </row>
-    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="63">
         <f t="shared" si="7"/>
         <v>18</v>
@@ -4152,11 +4153,11 @@
         <v>4.28</v>
       </c>
       <c r="E23" s="73">
-        <v>212551.18</v>
-      </c>
-      <c r="F23" s="74">
-        <f>E23+RESUMEN!D59</f>
-        <v>272551.18</v>
+        <v>182511.18</v>
+      </c>
+      <c r="F23" s="242">
+        <f>E23+RESUMEN!D58</f>
+        <v>242511.18</v>
       </c>
       <c r="G23" s="75">
         <f t="shared" si="0"/>
@@ -4200,7 +4201,7 @@
       <c r="T23" s="164"/>
       <c r="U23" s="164"/>
     </row>
-    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="63"/>
       <c r="B24" s="63"/>
       <c r="C24" s="64"/>
@@ -4221,7 +4222,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="82"/>
       <c r="B25" s="63"/>
       <c r="C25" s="64"/>
@@ -4239,7 +4240,7 @@
       <c r="O25" s="81"/>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="1:21" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" ht="22.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="82"/>
       <c r="B26" s="65"/>
       <c r="C26" s="64"/>
@@ -4257,7 +4258,7 @@
       <c r="O26" s="81"/>
       <c r="P26" s="42"/>
     </row>
-    <row r="27" spans="1:21" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="83"/>
       <c r="B27" s="63"/>
       <c r="C27" s="64"/>
@@ -4275,7 +4276,7 @@
       <c r="O27" s="81"/>
       <c r="P27" s="42"/>
     </row>
-    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="63"/>
       <c r="B28" s="89"/>
       <c r="C28" s="89"/>
@@ -4293,7 +4294,7 @@
       <c r="O28" s="92"/>
       <c r="P28" s="42"/>
     </row>
-    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="93"/>
       <c r="B29" s="94"/>
       <c r="C29" s="94"/>
@@ -4303,146 +4304,140 @@
       </c>
       <c r="E29" s="52">
         <f>SUM(E6:E28)</f>
-        <v>9022054.7100000009</v>
+        <v>10018461.710000001</v>
       </c>
       <c r="F29" s="61">
         <f>SUM(F6:F28)</f>
-        <v>4938034.42</v>
+        <v>4404558.63</v>
       </c>
       <c r="G29" s="61">
         <f>SUM(G6:G28)</f>
-        <v>4084020.29</v>
+        <v>5613903.080000001</v>
       </c>
       <c r="H29" s="61">
-        <f t="shared" ref="H29:N29" si="11">SUM(H6:H28)</f>
-        <v>131820.60869999998</v>
+        <f t="shared" ref="H29:N29" si="10">SUM(H6:H28)</f>
+        <v>177717.09239999999</v>
       </c>
       <c r="I29" s="61">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J29" s="131">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>5584473.3774959994</v>
       </c>
       <c r="K29" s="131"/>
       <c r="L29" s="61">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>86203.467647999991</v>
       </c>
       <c r="M29" s="96">
         <f>SUM(M6:M23)</f>
-        <v>10010019.710000001</v>
+        <v>11585800.709999999</v>
       </c>
       <c r="N29" s="96">
-        <f t="shared" si="11"/>
-        <v>10610624.710000001</v>
+        <f t="shared" si="10"/>
+        <v>12280951.709999999</v>
       </c>
       <c r="O29" s="96">
         <f>SUM(O6:O28)</f>
-        <v>10310320.710000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11933373.709999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="49"/>
       <c r="C30" s="49"/>
     </row>
-    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="216" t="str">
+    <row r="31" spans="1:21" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="208" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="216"/>
-      <c r="D32" s="216"/>
-      <c r="E32" s="216"/>
-      <c r="F32" s="216"/>
-      <c r="G32" s="216"/>
-      <c r="H32" s="216"/>
-      <c r="I32" s="216"/>
-      <c r="J32" s="216"/>
-      <c r="K32" s="216"/>
-      <c r="L32" s="216"/>
-      <c r="M32" s="216"/>
-    </row>
-    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="216"/>
-      <c r="C33" s="216"/>
-      <c r="D33" s="216"/>
-      <c r="E33" s="216"/>
-      <c r="F33" s="216"/>
-      <c r="G33" s="216"/>
-      <c r="H33" s="216"/>
-      <c r="I33" s="216"/>
-      <c r="J33" s="216"/>
-      <c r="K33" s="216"/>
-      <c r="L33" s="216"/>
-      <c r="M33" s="216"/>
-    </row>
-    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="216"/>
-      <c r="C34" s="216"/>
-      <c r="D34" s="216"/>
-      <c r="E34" s="216"/>
-      <c r="F34" s="216"/>
-      <c r="G34" s="216"/>
-      <c r="H34" s="216"/>
-      <c r="I34" s="216"/>
-      <c r="J34" s="216"/>
-      <c r="K34" s="216"/>
-      <c r="L34" s="216"/>
-      <c r="M34" s="216"/>
-    </row>
-    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="216"/>
-      <c r="C35" s="216"/>
-      <c r="D35" s="216"/>
-      <c r="E35" s="216"/>
-      <c r="F35" s="216"/>
-      <c r="G35" s="216"/>
-      <c r="H35" s="216"/>
-      <c r="I35" s="216"/>
-      <c r="J35" s="216"/>
-      <c r="K35" s="216"/>
-      <c r="L35" s="216"/>
-      <c r="M35" s="216"/>
-    </row>
-    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="216"/>
-      <c r="C36" s="216"/>
-      <c r="D36" s="216"/>
-      <c r="E36" s="216"/>
-      <c r="F36" s="216"/>
-      <c r="G36" s="216"/>
-      <c r="H36" s="216"/>
-      <c r="I36" s="216"/>
-      <c r="J36" s="216"/>
-      <c r="K36" s="216"/>
-      <c r="L36" s="216"/>
-      <c r="M36" s="216"/>
-    </row>
-    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="216"/>
-      <c r="C37" s="216"/>
-      <c r="D37" s="216"/>
-      <c r="E37" s="216"/>
-      <c r="F37" s="216"/>
-      <c r="G37" s="216"/>
-      <c r="H37" s="216"/>
-      <c r="I37" s="216"/>
-      <c r="J37" s="216"/>
-      <c r="K37" s="216"/>
-      <c r="L37" s="216"/>
-      <c r="M37" s="216"/>
+      <c r="C32" s="208"/>
+      <c r="D32" s="208"/>
+      <c r="E32" s="208"/>
+      <c r="F32" s="208"/>
+      <c r="G32" s="208"/>
+      <c r="H32" s="208"/>
+      <c r="I32" s="208"/>
+      <c r="J32" s="208"/>
+      <c r="K32" s="208"/>
+      <c r="L32" s="208"/>
+      <c r="M32" s="208"/>
+    </row>
+    <row r="33" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="208"/>
+      <c r="C33" s="208"/>
+      <c r="D33" s="208"/>
+      <c r="E33" s="208"/>
+      <c r="F33" s="208"/>
+      <c r="G33" s="208"/>
+      <c r="H33" s="208"/>
+      <c r="I33" s="208"/>
+      <c r="J33" s="208"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
+      <c r="M33" s="208"/>
+    </row>
+    <row r="34" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="208"/>
+      <c r="C34" s="208"/>
+      <c r="D34" s="208"/>
+      <c r="E34" s="208"/>
+      <c r="F34" s="208"/>
+      <c r="G34" s="208"/>
+      <c r="H34" s="208"/>
+      <c r="I34" s="208"/>
+      <c r="J34" s="208"/>
+      <c r="K34" s="208"/>
+      <c r="L34" s="208"/>
+      <c r="M34" s="208"/>
+    </row>
+    <row r="35" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="208"/>
+      <c r="C35" s="208"/>
+      <c r="D35" s="208"/>
+      <c r="E35" s="208"/>
+      <c r="F35" s="208"/>
+      <c r="G35" s="208"/>
+      <c r="H35" s="208"/>
+      <c r="I35" s="208"/>
+      <c r="J35" s="208"/>
+      <c r="K35" s="208"/>
+      <c r="L35" s="208"/>
+      <c r="M35" s="208"/>
+    </row>
+    <row r="36" spans="2:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="208"/>
+      <c r="C36" s="208"/>
+      <c r="D36" s="208"/>
+      <c r="E36" s="208"/>
+      <c r="F36" s="208"/>
+      <c r="G36" s="208"/>
+      <c r="H36" s="208"/>
+      <c r="I36" s="208"/>
+      <c r="J36" s="208"/>
+      <c r="K36" s="208"/>
+      <c r="L36" s="208"/>
+      <c r="M36" s="208"/>
+    </row>
+    <row r="37" spans="2:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="208"/>
+      <c r="C37" s="208"/>
+      <c r="D37" s="208"/>
+      <c r="E37" s="208"/>
+      <c r="F37" s="208"/>
+      <c r="G37" s="208"/>
+      <c r="H37" s="208"/>
+      <c r="I37" s="208"/>
+      <c r="J37" s="208"/>
+      <c r="K37" s="208"/>
+      <c r="L37" s="208"/>
+      <c r="M37" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B32:M37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="H4:H5"/>
@@ -4453,6 +4448,12 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="B32:M37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4462,10 +4463,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B2" s="169" t="s">
         <v>103</v>
       </c>
@@ -4476,7 +4477,7 @@
       <c r="E2" s="166"/>
       <c r="F2" s="167"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B3" s="171" t="s">
         <v>104</v>
       </c>
@@ -4485,7 +4486,7 @@
       </c>
       <c r="F3" s="168"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B4" s="233" t="s">
         <v>106</v>
       </c>
@@ -4494,14 +4495,14 @@
       <c r="E4" s="234"/>
       <c r="F4" s="235"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B5" s="233"/>
       <c r="C5" s="234"/>
       <c r="D5" s="234"/>
       <c r="E5" s="234"/>
       <c r="F5" s="235"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="122"/>
       <c r="B6" s="233"/>
       <c r="C6" s="234"/>
@@ -4511,7 +4512,7 @@
       <c r="N6" s="122"/>
       <c r="O6" s="122"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="122"/>
       <c r="B7" s="233"/>
       <c r="C7" s="234"/>
@@ -4521,7 +4522,7 @@
       <c r="N7" s="122"/>
       <c r="O7" s="122"/>
     </row>
-    <row r="8" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="122"/>
       <c r="B8" s="236"/>
       <c r="C8" s="237"/>
@@ -4531,12 +4532,12 @@
       <c r="N8" s="122"/>
       <c r="O8" s="122"/>
     </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="122"/>
       <c r="N9" s="122"/>
       <c r="O9" s="122"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="122"/>
       <c r="B10" s="173" t="s">
         <v>103</v>
@@ -4550,7 +4551,7 @@
       <c r="N10" s="122"/>
       <c r="O10" s="122"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="122"/>
       <c r="B11" s="175" t="s">
         <v>104</v>
@@ -4562,7 +4563,7 @@
       <c r="N11" s="122"/>
       <c r="O11" s="122"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B12" s="233" t="s">
         <v>108</v>
       </c>
@@ -4571,28 +4572,28 @@
       <c r="E12" s="234"/>
       <c r="F12" s="235"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B13" s="233"/>
       <c r="C13" s="234"/>
       <c r="D13" s="234"/>
       <c r="E13" s="234"/>
       <c r="F13" s="235"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14" s="233"/>
       <c r="C14" s="234"/>
       <c r="D14" s="234"/>
       <c r="E14" s="234"/>
       <c r="F14" s="235"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15" s="233"/>
       <c r="C15" s="234"/>
       <c r="D15" s="234"/>
       <c r="E15" s="234"/>
       <c r="F15" s="235"/>
     </row>
-    <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="236"/>
       <c r="C16" s="237"/>
       <c r="D16" s="237"/>

--- a/2026/YRIGOYEN 7630/Septiembre/YRIGOYEN7630-Septiembre.xlsx
+++ b/2026/YRIGOYEN 7630/Septiembre/YRIGOYEN7630-Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803F7276-6A4D-4F18-8916-DB37C0CD7214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACECA92-B17E-4AB1-9D9A-2A6A4A7F2964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1428,34 +1428,82 @@
     </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1464,51 +1512,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1526,9 +1529,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1963,12 +1963,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="222" t="s">
+      <c r="B3" s="218" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="223"/>
+      <c r="C3" s="218"/>
+      <c r="D3" s="218"/>
+      <c r="E3" s="219"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -2006,49 +2006,49 @@
       <c r="E6" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="225" t="s">
+      <c r="B8" s="221" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="225"/>
+      <c r="C8" s="221"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="225"/>
-      <c r="C9" s="225"/>
+      <c r="B9" s="221"/>
+      <c r="C9" s="221"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="225"/>
-      <c r="C10" s="225"/>
+      <c r="B10" s="221"/>
+      <c r="C10" s="221"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="224" t="s">
+      <c r="A13" s="220" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="224"/>
-      <c r="C13" s="224"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="224"/>
+      <c r="B13" s="220"/>
+      <c r="C13" s="220"/>
+      <c r="D13" s="220"/>
+      <c r="E13" s="220"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="224"/>
-      <c r="B14" s="224"/>
-      <c r="C14" s="224"/>
-      <c r="D14" s="224"/>
-      <c r="E14" s="224"/>
+      <c r="A14" s="220"/>
+      <c r="B14" s="220"/>
+      <c r="C14" s="220"/>
+      <c r="D14" s="220"/>
+      <c r="E14" s="220"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="224"/>
-      <c r="B15" s="224"/>
-      <c r="C15" s="224"/>
-      <c r="D15" s="224"/>
-      <c r="E15" s="224"/>
+      <c r="A15" s="220"/>
+      <c r="B15" s="220"/>
+      <c r="C15" s="220"/>
+      <c r="D15" s="220"/>
+      <c r="E15" s="220"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="224"/>
-      <c r="B16" s="224"/>
-      <c r="C16" s="224"/>
-      <c r="D16" s="224"/>
-      <c r="E16" s="224"/>
+      <c r="A16" s="220"/>
+      <c r="B16" s="220"/>
+      <c r="C16" s="220"/>
+      <c r="D16" s="220"/>
+      <c r="E16" s="220"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D17" s="109"/>
@@ -2184,10 +2184,10 @@
       <c r="E31" s="137"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="218" t="s">
+      <c r="A32" s="216" t="s">
         <v>116</v>
       </c>
-      <c r="B32" s="219"/>
+      <c r="B32" s="217"/>
       <c r="C32" s="51"/>
       <c r="D32" s="177">
         <v>50000</v>
@@ -2195,10 +2195,10 @@
       <c r="E32" s="138"/>
     </row>
     <row r="33" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="218" t="s">
+      <c r="A33" s="216" t="s">
         <v>128</v>
       </c>
-      <c r="B33" s="219"/>
+      <c r="B33" s="217"/>
       <c r="C33" s="51"/>
       <c r="D33" s="212">
         <v>180000</v>
@@ -2233,10 +2233,10 @@
       <c r="E35" s="140"/>
     </row>
     <row r="36" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="216" t="s">
+      <c r="A36" s="222" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="217"/>
+      <c r="B36" s="223"/>
       <c r="C36" s="53"/>
       <c r="D36" s="213">
         <f>30025+7909</f>
@@ -2247,10 +2247,10 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="218" t="s">
+      <c r="A37" s="216" t="s">
         <v>89</v>
       </c>
-      <c r="B37" s="219"/>
+      <c r="B37" s="217"/>
       <c r="C37" s="53"/>
       <c r="D37" s="214">
         <v>69628</v>
@@ -2444,10 +2444,10 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="216" t="s">
+      <c r="A52" s="222" t="s">
         <v>75</v>
       </c>
-      <c r="B52" s="217"/>
+      <c r="B52" s="223"/>
       <c r="C52" s="5"/>
       <c r="D52" s="152">
         <v>530549.97</v>
@@ -2529,10 +2529,10 @@
       </c>
     </row>
     <row r="59" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="216" t="s">
+      <c r="A59" s="222" t="s">
         <v>111</v>
       </c>
-      <c r="B59" s="217"/>
+      <c r="B59" s="223"/>
       <c r="C59" s="5"/>
       <c r="D59" s="103">
         <v>60600</v>
@@ -2666,22 +2666,22 @@
       <c r="E71" s="114"/>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="216"/>
-      <c r="B72" s="217"/>
+      <c r="A72" s="222"/>
+      <c r="B72" s="223"/>
       <c r="C72" s="5"/>
       <c r="D72" s="124"/>
       <c r="E72" s="101"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="216"/>
-      <c r="B73" s="217"/>
+      <c r="A73" s="222"/>
+      <c r="B73" s="223"/>
       <c r="C73" s="5"/>
       <c r="D73" s="103"/>
       <c r="E73" s="101"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="218"/>
-      <c r="B74" s="219"/>
+      <c r="A74" s="216"/>
+      <c r="B74" s="217"/>
       <c r="C74" s="5"/>
       <c r="D74" s="103"/>
       <c r="E74" s="101"/>
@@ -2953,16 +2953,16 @@
     </row>
     <row r="112" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="221" t="s">
+      <c r="A113" s="225" t="s">
         <v>32</v>
       </c>
-      <c r="B113" s="221"/>
-      <c r="C113" s="221"/>
+      <c r="B113" s="225"/>
+      <c r="C113" s="225"/>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="221"/>
-      <c r="B114" s="221"/>
-      <c r="C114" s="221"/>
+      <c r="A114" s="225"/>
+      <c r="B114" s="225"/>
+      <c r="C114" s="225"/>
     </row>
     <row r="115" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="116"/>
@@ -2992,40 +2992,35 @@
       <c r="M118" s="8"/>
     </row>
     <row r="119" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="220"/>
-      <c r="B119" s="220"/>
-      <c r="C119" s="220"/>
-      <c r="D119" s="220"/>
-      <c r="E119" s="220"/>
+      <c r="A119" s="224"/>
+      <c r="B119" s="224"/>
+      <c r="C119" s="224"/>
+      <c r="D119" s="224"/>
+      <c r="E119" s="224"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="220"/>
-      <c r="B120" s="220"/>
-      <c r="C120" s="220"/>
-      <c r="D120" s="220"/>
-      <c r="E120" s="220"/>
+      <c r="A120" s="224"/>
+      <c r="B120" s="224"/>
+      <c r="C120" s="224"/>
+      <c r="D120" s="224"/>
+      <c r="E120" s="224"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="220"/>
-      <c r="B121" s="220"/>
-      <c r="C121" s="220"/>
-      <c r="D121" s="220"/>
-      <c r="E121" s="220"/>
+      <c r="A121" s="224"/>
+      <c r="B121" s="224"/>
+      <c r="C121" s="224"/>
+      <c r="D121" s="224"/>
+      <c r="E121" s="224"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A122" s="220"/>
-      <c r="B122" s="220"/>
-      <c r="C122" s="220"/>
-      <c r="D122" s="220"/>
-      <c r="E122" s="220"/>
+      <c r="A122" s="224"/>
+      <c r="B122" s="224"/>
+      <c r="C122" s="224"/>
+      <c r="D122" s="224"/>
+      <c r="E122" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="B8:C10"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A52:B52"/>
@@ -3035,6 +3030,11 @@
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="B8:C10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3070,17 +3070,17 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="231"/>
-      <c r="E1" s="231"/>
-      <c r="F1" s="231"/>
-      <c r="G1" s="231"/>
-      <c r="H1" s="231"/>
-      <c r="I1" s="231"/>
-      <c r="J1" s="231"/>
-      <c r="K1" s="231"/>
-      <c r="L1" s="231"/>
-      <c r="M1" s="231"/>
-      <c r="N1" s="231"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="227"/>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
     </row>
@@ -3130,63 +3130,63 @@
       <c r="P3" s="58"/>
     </row>
     <row r="4" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="237" t="s">
+      <c r="A4" s="236" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="238"/>
-      <c r="C4" s="238"/>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
-      <c r="H4" s="238"/>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="M4" s="238"/>
-      <c r="N4" s="238"/>
-      <c r="O4" s="238"/>
-      <c r="P4" s="239"/>
+      <c r="B4" s="237"/>
+      <c r="C4" s="237"/>
+      <c r="D4" s="237"/>
+      <c r="E4" s="237"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
+      <c r="H4" s="237"/>
+      <c r="I4" s="237"/>
+      <c r="J4" s="237"/>
+      <c r="K4" s="237"/>
+      <c r="L4" s="237"/>
+      <c r="M4" s="237"/>
+      <c r="N4" s="237"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="238"/>
     </row>
     <row r="5" spans="1:19" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="240"/>
-      <c r="B5" s="241"/>
-      <c r="C5" s="241"/>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="M5" s="241"/>
-      <c r="N5" s="241"/>
-      <c r="O5" s="241"/>
-      <c r="P5" s="242"/>
+      <c r="A5" s="239"/>
+      <c r="B5" s="240"/>
+      <c r="C5" s="240"/>
+      <c r="D5" s="240"/>
+      <c r="E5" s="240"/>
+      <c r="F5" s="240"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="240"/>
+      <c r="I5" s="240"/>
+      <c r="J5" s="240"/>
+      <c r="K5" s="240"/>
+      <c r="L5" s="240"/>
+      <c r="M5" s="240"/>
+      <c r="N5" s="240"/>
+      <c r="O5" s="240"/>
+      <c r="P5" s="241"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="226" t="s">
+      <c r="A6" s="242" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="226" t="s">
+      <c r="B6" s="242" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="226" t="s">
+      <c r="C6" s="242" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="226" t="s">
+      <c r="D6" s="242" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="228" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="249" t="s">
+      <c r="F6" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="233" t="s">
+      <c r="G6" s="232" t="s">
         <v>30</v>
       </c>
       <c r="H6" s="228" t="s">
@@ -3204,16 +3204,16 @@
       <c r="L6" s="228" t="s">
         <v>129</v>
       </c>
-      <c r="M6" s="235" t="s">
+      <c r="M6" s="234" t="s">
         <v>80</v>
       </c>
       <c r="N6" s="193" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="232" t="s">
+      <c r="O6" s="230" t="s">
         <v>25</v>
       </c>
-      <c r="P6" s="230" t="s">
+      <c r="P6" s="226" t="s">
         <v>36</v>
       </c>
       <c r="S6" s="126">
@@ -3221,25 +3221,25 @@
       </c>
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="226"/>
-      <c r="B7" s="226"/>
-      <c r="C7" s="227"/>
-      <c r="D7" s="226"/>
+      <c r="A7" s="242"/>
+      <c r="B7" s="242"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="242"/>
       <c r="E7" s="229"/>
-      <c r="F7" s="249"/>
-      <c r="G7" s="234"/>
+      <c r="F7" s="231"/>
+      <c r="G7" s="233"/>
       <c r="H7" s="229"/>
       <c r="I7" s="228"/>
       <c r="J7" s="229"/>
       <c r="K7" s="229"/>
       <c r="L7" s="229"/>
-      <c r="M7" s="236"/>
+      <c r="M7" s="235"/>
       <c r="N7" s="59" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O7" s="232"/>
-      <c r="P7" s="230"/>
+      <c r="O7" s="230"/>
+      <c r="P7" s="226"/>
     </row>
     <row r="8" spans="1:19" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="159">
@@ -3599,7 +3599,7 @@
         <v>5.67</v>
       </c>
       <c r="E14" s="203">
-        <v>1144136.07</v>
+        <v>515000</v>
       </c>
       <c r="F14" s="203">
         <f>670000-155000</f>
@@ -3607,11 +3607,10 @@
       </c>
       <c r="G14" s="204">
         <f t="shared" si="0"/>
-        <v>629136.07000000007</v>
+        <v>0</v>
       </c>
       <c r="H14" s="204">
-        <f t="shared" si="2"/>
-        <v>18874.0821</v>
+        <v>0</v>
       </c>
       <c r="I14" s="205">
         <v>0</v>
@@ -3630,15 +3629,15 @@
       </c>
       <c r="N14" s="208">
         <f t="shared" si="4"/>
-        <v>1149281.07</v>
+        <v>501270.07</v>
       </c>
       <c r="O14" s="209">
         <f t="shared" si="5"/>
-        <v>1218238.07</v>
+        <v>531346.06999999995</v>
       </c>
       <c r="P14" s="210">
         <f t="shared" si="6"/>
-        <v>1183759.07</v>
+        <v>516308.07</v>
       </c>
       <c r="Q14" s="42">
         <f t="shared" si="8"/>
@@ -4408,7 +4407,7 @@
       </c>
       <c r="E31" s="52">
         <f>SUM(E8:E30)</f>
-        <v>10032128.710000001</v>
+        <v>9402992.6400000006</v>
       </c>
       <c r="F31" s="60">
         <f>SUM(F8:F30)</f>
@@ -4416,11 +4415,11 @@
       </c>
       <c r="G31" s="60">
         <f>SUM(G8:G30)</f>
-        <v>4643345.03</v>
+        <v>4014208.96</v>
       </c>
       <c r="H31" s="60">
         <f t="shared" ref="H31:O31" si="10">SUM(H8:H30)</f>
-        <v>148600.35090000002</v>
+        <v>129726.26879999999</v>
       </c>
       <c r="I31" s="60">
         <f t="shared" si="10"/>
@@ -4438,15 +4437,15 @@
       </c>
       <c r="N31" s="94">
         <f>SUM(N8:N25)</f>
-        <v>10766125.710000001</v>
+        <v>10118114.710000001</v>
       </c>
       <c r="O31" s="94">
         <f t="shared" si="10"/>
-        <v>11412096.709999999</v>
+        <v>10725204.709999999</v>
       </c>
       <c r="P31" s="94">
         <f>SUM(P8:P30)</f>
-        <v>11089108.710000001</v>
+        <v>10421657.710000001</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4455,100 +4454,107 @@
     </row>
     <row r="33" spans="2:14" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:14" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="220" t="str">
+      <c r="B34" s="224" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C34" s="220"/>
-      <c r="D34" s="220"/>
-      <c r="E34" s="220"/>
-      <c r="F34" s="220"/>
-      <c r="G34" s="220"/>
-      <c r="H34" s="220"/>
-      <c r="I34" s="220"/>
-      <c r="J34" s="220"/>
-      <c r="K34" s="220"/>
-      <c r="L34" s="220"/>
-      <c r="M34" s="220"/>
-      <c r="N34" s="220"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="224"/>
+      <c r="F34" s="224"/>
+      <c r="G34" s="224"/>
+      <c r="H34" s="224"/>
+      <c r="I34" s="224"/>
+      <c r="J34" s="224"/>
+      <c r="K34" s="224"/>
+      <c r="L34" s="224"/>
+      <c r="M34" s="224"/>
+      <c r="N34" s="224"/>
     </row>
     <row r="35" spans="2:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="220"/>
-      <c r="C35" s="220"/>
-      <c r="D35" s="220"/>
-      <c r="E35" s="220"/>
-      <c r="F35" s="220"/>
-      <c r="G35" s="220"/>
-      <c r="H35" s="220"/>
-      <c r="I35" s="220"/>
-      <c r="J35" s="220"/>
-      <c r="K35" s="220"/>
-      <c r="L35" s="220"/>
-      <c r="M35" s="220"/>
-      <c r="N35" s="220"/>
+      <c r="B35" s="224"/>
+      <c r="C35" s="224"/>
+      <c r="D35" s="224"/>
+      <c r="E35" s="224"/>
+      <c r="F35" s="224"/>
+      <c r="G35" s="224"/>
+      <c r="H35" s="224"/>
+      <c r="I35" s="224"/>
+      <c r="J35" s="224"/>
+      <c r="K35" s="224"/>
+      <c r="L35" s="224"/>
+      <c r="M35" s="224"/>
+      <c r="N35" s="224"/>
     </row>
     <row r="36" spans="2:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="220"/>
-      <c r="C36" s="220"/>
-      <c r="D36" s="220"/>
-      <c r="E36" s="220"/>
-      <c r="F36" s="220"/>
-      <c r="G36" s="220"/>
-      <c r="H36" s="220"/>
-      <c r="I36" s="220"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="220"/>
-      <c r="L36" s="220"/>
-      <c r="M36" s="220"/>
-      <c r="N36" s="220"/>
+      <c r="B36" s="224"/>
+      <c r="C36" s="224"/>
+      <c r="D36" s="224"/>
+      <c r="E36" s="224"/>
+      <c r="F36" s="224"/>
+      <c r="G36" s="224"/>
+      <c r="H36" s="224"/>
+      <c r="I36" s="224"/>
+      <c r="J36" s="224"/>
+      <c r="K36" s="224"/>
+      <c r="L36" s="224"/>
+      <c r="M36" s="224"/>
+      <c r="N36" s="224"/>
     </row>
     <row r="37" spans="2:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="220"/>
-      <c r="C37" s="220"/>
-      <c r="D37" s="220"/>
-      <c r="E37" s="220"/>
-      <c r="F37" s="220"/>
-      <c r="G37" s="220"/>
-      <c r="H37" s="220"/>
-      <c r="I37" s="220"/>
-      <c r="J37" s="220"/>
-      <c r="K37" s="220"/>
-      <c r="L37" s="220"/>
-      <c r="M37" s="220"/>
-      <c r="N37" s="220"/>
+      <c r="B37" s="224"/>
+      <c r="C37" s="224"/>
+      <c r="D37" s="224"/>
+      <c r="E37" s="224"/>
+      <c r="F37" s="224"/>
+      <c r="G37" s="224"/>
+      <c r="H37" s="224"/>
+      <c r="I37" s="224"/>
+      <c r="J37" s="224"/>
+      <c r="K37" s="224"/>
+      <c r="L37" s="224"/>
+      <c r="M37" s="224"/>
+      <c r="N37" s="224"/>
     </row>
     <row r="38" spans="2:14" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="220"/>
-      <c r="C38" s="220"/>
-      <c r="D38" s="220"/>
-      <c r="E38" s="220"/>
-      <c r="F38" s="220"/>
-      <c r="G38" s="220"/>
-      <c r="H38" s="220"/>
-      <c r="I38" s="220"/>
-      <c r="J38" s="220"/>
-      <c r="K38" s="220"/>
-      <c r="L38" s="220"/>
-      <c r="M38" s="220"/>
-      <c r="N38" s="220"/>
+      <c r="B38" s="224"/>
+      <c r="C38" s="224"/>
+      <c r="D38" s="224"/>
+      <c r="E38" s="224"/>
+      <c r="F38" s="224"/>
+      <c r="G38" s="224"/>
+      <c r="H38" s="224"/>
+      <c r="I38" s="224"/>
+      <c r="J38" s="224"/>
+      <c r="K38" s="224"/>
+      <c r="L38" s="224"/>
+      <c r="M38" s="224"/>
+      <c r="N38" s="224"/>
     </row>
     <row r="39" spans="2:14" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="220"/>
-      <c r="C39" s="220"/>
-      <c r="D39" s="220"/>
-      <c r="E39" s="220"/>
-      <c r="F39" s="220"/>
-      <c r="G39" s="220"/>
-      <c r="H39" s="220"/>
-      <c r="I39" s="220"/>
-      <c r="J39" s="220"/>
-      <c r="K39" s="220"/>
-      <c r="L39" s="220"/>
-      <c r="M39" s="220"/>
-      <c r="N39" s="220"/>
+      <c r="B39" s="224"/>
+      <c r="C39" s="224"/>
+      <c r="D39" s="224"/>
+      <c r="E39" s="224"/>
+      <c r="F39" s="224"/>
+      <c r="G39" s="224"/>
+      <c r="H39" s="224"/>
+      <c r="I39" s="224"/>
+      <c r="J39" s="224"/>
+      <c r="K39" s="224"/>
+      <c r="L39" s="224"/>
+      <c r="M39" s="224"/>
+      <c r="N39" s="224"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B34:N39"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="D1:N1"/>
     <mergeCell ref="H6:H7"/>
@@ -4560,13 +4566,6 @@
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="A4:P5"/>
-    <mergeCell ref="B34:N39"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -4600,48 +4599,48 @@
       <c r="F3" s="166"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="244"/>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="245"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="246"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="243"/>
-      <c r="C5" s="244"/>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="245"/>
+      <c r="B5" s="244"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="246"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="120"/>
-      <c r="B6" s="243"/>
-      <c r="C6" s="244"/>
-      <c r="D6" s="244"/>
-      <c r="E6" s="244"/>
-      <c r="F6" s="245"/>
+      <c r="B6" s="244"/>
+      <c r="C6" s="245"/>
+      <c r="D6" s="245"/>
+      <c r="E6" s="245"/>
+      <c r="F6" s="246"/>
       <c r="N6" s="120"/>
       <c r="O6" s="120"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="120"/>
-      <c r="B7" s="243"/>
-      <c r="C7" s="244"/>
-      <c r="D7" s="244"/>
-      <c r="E7" s="244"/>
-      <c r="F7" s="245"/>
+      <c r="B7" s="244"/>
+      <c r="C7" s="245"/>
+      <c r="D7" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="246"/>
       <c r="N7" s="120"/>
       <c r="O7" s="120"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="120"/>
-      <c r="B8" s="246"/>
-      <c r="C8" s="247"/>
-      <c r="D8" s="247"/>
-      <c r="E8" s="247"/>
-      <c r="F8" s="248"/>
+      <c r="B8" s="247"/>
+      <c r="C8" s="248"/>
+      <c r="D8" s="248"/>
+      <c r="E8" s="248"/>
+      <c r="F8" s="249"/>
       <c r="N8" s="120"/>
       <c r="O8" s="120"/>
     </row>
@@ -4677,41 +4676,41 @@
       <c r="O11" s="120"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="243" t="s">
+      <c r="B12" s="244" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="244"/>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="245"/>
+      <c r="C12" s="245"/>
+      <c r="D12" s="245"/>
+      <c r="E12" s="245"/>
+      <c r="F12" s="246"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="243"/>
-      <c r="C13" s="244"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="245"/>
+      <c r="B13" s="244"/>
+      <c r="C13" s="245"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="246"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="243"/>
-      <c r="C14" s="244"/>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="245"/>
+      <c r="B14" s="244"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="246"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="243"/>
-      <c r="C15" s="244"/>
-      <c r="D15" s="244"/>
-      <c r="E15" s="244"/>
-      <c r="F15" s="245"/>
+      <c r="B15" s="244"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
+      <c r="F15" s="246"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="246"/>
-      <c r="C16" s="247"/>
-      <c r="D16" s="247"/>
-      <c r="E16" s="247"/>
-      <c r="F16" s="248"/>
+      <c r="B16" s="247"/>
+      <c r="C16" s="248"/>
+      <c r="D16" s="248"/>
+      <c r="E16" s="248"/>
+      <c r="F16" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2026/YRIGOYEN 7630/Septiembre/YRIGOYEN7630-Septiembre.xlsx
+++ b/2026/YRIGOYEN 7630/Septiembre/YRIGOYEN7630-Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\YRIGOYEN 7630\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACECA92-B17E-4AB1-9D9A-2A6A4A7F2964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78FCD55-6119-431B-89D8-9607E20CC5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3056,10 +3056,12 @@
     <col min="7" max="7" width="10.5703125" customWidth="1"/>
     <col min="8" max="8" width="9.5703125" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="12" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="14.28515625" customWidth="1"/>
     <col min="17" max="17" width="0.140625" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
@@ -4567,8 +4569,8 @@
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="A4:P5"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="90" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
